--- a/venta.xlsx
+++ b/venta.xlsx
@@ -7760,26 +7760,60 @@
       </c>
     </row>
     <row r="932" ht="15.75" customHeight="1">
-      <c r="A932" s="3"/>
-      <c r="B932" s="7"/>
+      <c r="A932" s="3">
+        <v>46222.0</v>
+      </c>
+      <c r="B932" s="6">
+        <v>7386.0</v>
+      </c>
     </row>
     <row r="933" ht="15.75" customHeight="1">
-      <c r="B933" s="7"/>
+      <c r="A933" s="3">
+        <v>46223.0</v>
+      </c>
+      <c r="B933" s="6">
+        <v>2164.0</v>
+      </c>
     </row>
     <row r="934" ht="15.75" customHeight="1">
-      <c r="B934" s="7"/>
+      <c r="A934" s="3">
+        <v>46224.0</v>
+      </c>
+      <c r="B934" s="6">
+        <v>2301.0</v>
+      </c>
     </row>
     <row r="935" ht="15.75" customHeight="1">
-      <c r="B935" s="7"/>
+      <c r="A935" s="3">
+        <v>46225.0</v>
+      </c>
+      <c r="B935" s="6">
+        <v>2299.0</v>
+      </c>
     </row>
     <row r="936" ht="15.75" customHeight="1">
-      <c r="B936" s="7"/>
+      <c r="A936" s="3">
+        <v>46226.0</v>
+      </c>
+      <c r="B936" s="6">
+        <v>2458.0</v>
+      </c>
     </row>
     <row r="937" ht="15.75" customHeight="1">
-      <c r="B937" s="7"/>
+      <c r="A937" s="3">
+        <v>46227.0</v>
+      </c>
+      <c r="B937" s="6">
+        <v>3098.0</v>
+      </c>
     </row>
     <row r="938" ht="15.75" customHeight="1">
-      <c r="B938" s="7"/>
+      <c r="A938" s="3">
+        <v>46228.0</v>
+      </c>
+      <c r="B938" s="6">
+        <v>3770.0</v>
+      </c>
     </row>
     <row r="939" ht="15.75" customHeight="1">
       <c r="B939" s="7"/>

--- a/venta.xlsx
+++ b/venta.xlsx
@@ -7812,29 +7812,64 @@
         <v>46228.0</v>
       </c>
       <c r="B938" s="6">
-        <v>3770.0</v>
+        <v>3795.0</v>
       </c>
     </row>
     <row r="939" ht="15.75" customHeight="1">
-      <c r="B939" s="7"/>
+      <c r="A939" s="3">
+        <v>46229.0</v>
+      </c>
+      <c r="B939" s="6">
+        <v>3350.0</v>
+      </c>
     </row>
     <row r="940" ht="15.75" customHeight="1">
-      <c r="B940" s="7"/>
+      <c r="A940" s="3">
+        <v>46230.0</v>
+      </c>
+      <c r="B940" s="6">
+        <v>2075.0</v>
+      </c>
     </row>
     <row r="941" ht="15.75" customHeight="1">
-      <c r="B941" s="7"/>
+      <c r="A941" s="3">
+        <v>46231.0</v>
+      </c>
+      <c r="B941" s="6">
+        <v>2289.0</v>
+      </c>
     </row>
     <row r="942" ht="15.75" customHeight="1">
-      <c r="B942" s="7"/>
+      <c r="A942" s="3">
+        <v>46232.0</v>
+      </c>
+      <c r="B942" s="6">
+        <v>2465.0</v>
+      </c>
     </row>
     <row r="943" ht="15.75" customHeight="1">
-      <c r="B943" s="7"/>
+      <c r="A943" s="3">
+        <v>46233.0</v>
+      </c>
+      <c r="B943" s="6">
+        <v>2423.0</v>
+      </c>
     </row>
     <row r="944" ht="15.75" customHeight="1">
-      <c r="B944" s="7"/>
+      <c r="A944" s="3">
+        <v>46234.0</v>
+      </c>
+      <c r="B944" s="6">
+        <v>4186.0</v>
+      </c>
     </row>
     <row r="945" ht="15.75" customHeight="1">
-      <c r="B945" s="7"/>
+      <c r="A945" s="3">
+        <v>46235.0</v>
+      </c>
+      <c r="B945" s="6">
+        <v>3955.0</v>
+      </c>
     </row>
     <row r="946" ht="15.75" customHeight="1">
       <c r="B946" s="7"/>

--- a/venta.xlsx
+++ b/venta.xlsx
@@ -7872,25 +7872,60 @@
       </c>
     </row>
     <row r="946" ht="15.75" customHeight="1">
-      <c r="B946" s="7"/>
+      <c r="A946" s="3">
+        <v>46236.0</v>
+      </c>
+      <c r="B946" s="6">
+        <v>4145.0</v>
+      </c>
     </row>
     <row r="947" ht="15.75" customHeight="1">
-      <c r="B947" s="7"/>
+      <c r="A947" s="3">
+        <v>46237.0</v>
+      </c>
+      <c r="B947" s="6">
+        <v>1901.0</v>
+      </c>
     </row>
     <row r="948" ht="15.75" customHeight="1">
-      <c r="B948" s="7"/>
+      <c r="A948" s="3">
+        <v>46238.0</v>
+      </c>
+      <c r="B948" s="6">
+        <v>2808.0</v>
+      </c>
     </row>
     <row r="949" ht="15.75" customHeight="1">
-      <c r="B949" s="7"/>
+      <c r="A949" s="3">
+        <v>46239.0</v>
+      </c>
+      <c r="B949" s="6">
+        <v>2090.0</v>
+      </c>
     </row>
     <row r="950" ht="15.75" customHeight="1">
-      <c r="B950" s="7"/>
+      <c r="A950" s="3">
+        <v>46240.0</v>
+      </c>
+      <c r="B950" s="6">
+        <v>2443.0</v>
+      </c>
     </row>
     <row r="951" ht="15.75" customHeight="1">
-      <c r="B951" s="7"/>
+      <c r="A951" s="3">
+        <v>46241.0</v>
+      </c>
+      <c r="B951" s="6">
+        <v>3390.0</v>
+      </c>
     </row>
     <row r="952" ht="15.75" customHeight="1">
-      <c r="B952" s="7"/>
+      <c r="A952" s="3">
+        <v>46242.0</v>
+      </c>
+      <c r="B952" s="6">
+        <v>3900.0</v>
+      </c>
     </row>
     <row r="953" ht="15.75" customHeight="1">
       <c r="B953" s="7"/>

--- a/venta.xlsx
+++ b/venta.xlsx
@@ -7928,48 +7928,119 @@
       </c>
     </row>
     <row r="953" ht="15.75" customHeight="1">
-      <c r="B953" s="7"/>
+      <c r="A953" s="3">
+        <v>46243.0</v>
+      </c>
+      <c r="B953" s="6">
+        <v>4121.0</v>
+      </c>
     </row>
     <row r="954" ht="15.75" customHeight="1">
-      <c r="B954" s="7"/>
+      <c r="A954" s="3">
+        <v>46244.0</v>
+      </c>
+      <c r="B954" s="6">
+        <v>2030.0</v>
+      </c>
     </row>
     <row r="955" ht="15.75" customHeight="1">
-      <c r="B955" s="7"/>
+      <c r="A955" s="3">
+        <v>46245.0</v>
+      </c>
+      <c r="B955" s="6">
+        <v>2758.0</v>
+      </c>
     </row>
     <row r="956" ht="15.75" customHeight="1">
-      <c r="B956" s="7"/>
+      <c r="A956" s="3">
+        <v>46246.0</v>
+      </c>
+      <c r="B956" s="6">
+        <v>3023.0</v>
+      </c>
     </row>
     <row r="957" ht="15.75" customHeight="1">
-      <c r="B957" s="7"/>
+      <c r="A957" s="3">
+        <v>46247.0</v>
+      </c>
+      <c r="B957" s="6">
+        <v>2654.0</v>
+      </c>
     </row>
     <row r="958" ht="15.75" customHeight="1">
-      <c r="B958" s="7"/>
+      <c r="A958" s="3">
+        <v>46248.0</v>
+      </c>
+      <c r="B958" s="6">
+        <v>3362.0</v>
+      </c>
     </row>
     <row r="959" ht="15.75" customHeight="1">
-      <c r="B959" s="7"/>
+      <c r="A959" s="3">
+        <v>46249.0</v>
+      </c>
+      <c r="B959" s="6">
+        <v>3523.0</v>
+      </c>
     </row>
     <row r="960" ht="15.75" customHeight="1">
-      <c r="B960" s="7"/>
+      <c r="A960" s="3">
+        <v>46250.0</v>
+      </c>
+      <c r="B960" s="6">
+        <v>3190.0</v>
+      </c>
     </row>
     <row r="961" ht="15.75" customHeight="1">
-      <c r="B961" s="7"/>
+      <c r="A961" s="3">
+        <v>46251.0</v>
+      </c>
+      <c r="B961" s="6">
+        <v>2105.0</v>
+      </c>
     </row>
     <row r="962" ht="15.75" customHeight="1">
-      <c r="B962" s="7"/>
+      <c r="A962" s="3">
+        <v>46252.0</v>
+      </c>
+      <c r="B962" s="6">
+        <v>3951.0</v>
+      </c>
     </row>
     <row r="963" ht="15.75" customHeight="1">
-      <c r="B963" s="7"/>
+      <c r="A963" s="3">
+        <v>46253.0</v>
+      </c>
+      <c r="B963" s="6">
+        <v>4105.0</v>
+      </c>
     </row>
     <row r="964" ht="15.75" customHeight="1">
-      <c r="B964" s="7"/>
+      <c r="A964" s="3">
+        <v>46254.0</v>
+      </c>
+      <c r="B964" s="6">
+        <v>2141.0</v>
+      </c>
     </row>
     <row r="965" ht="15.75" customHeight="1">
-      <c r="B965" s="7"/>
+      <c r="A965" s="3">
+        <v>46255.0</v>
+      </c>
+      <c r="B965" s="6">
+        <v>3162.0</v>
+      </c>
     </row>
     <row r="966" ht="15.75" customHeight="1">
-      <c r="B966" s="7"/>
+      <c r="A966" s="3">
+        <v>46256.0</v>
+      </c>
+      <c r="B966" s="6">
+        <v>3470.0</v>
+      </c>
     </row>
     <row r="967" ht="15.75" customHeight="1">
+      <c r="A967" s="3"/>
       <c r="B967" s="7"/>
     </row>
     <row r="968" ht="15.75" customHeight="1">

--- a/venta.xlsx
+++ b/venta.xlsx
@@ -8040,68 +8040,172 @@
       </c>
     </row>
     <row r="967" ht="15.75" customHeight="1">
-      <c r="A967" s="3"/>
-      <c r="B967" s="7"/>
+      <c r="A967" s="3">
+        <v>46257.0</v>
+      </c>
+      <c r="B967" s="6">
+        <v>3913.0</v>
+      </c>
     </row>
     <row r="968" ht="15.75" customHeight="1">
-      <c r="B968" s="7"/>
+      <c r="A968" s="3">
+        <v>46258.0</v>
+      </c>
+      <c r="B968" s="6">
+        <v>2347.0</v>
+      </c>
     </row>
     <row r="969" ht="15.75" customHeight="1">
-      <c r="B969" s="7"/>
+      <c r="A969" s="3">
+        <v>46259.0</v>
+      </c>
+      <c r="B969" s="6">
+        <v>2297.0</v>
+      </c>
     </row>
     <row r="970" ht="15.75" customHeight="1">
-      <c r="B970" s="7"/>
+      <c r="A970" s="3">
+        <v>46260.0</v>
+      </c>
+      <c r="B970" s="6">
+        <v>1953.0</v>
+      </c>
     </row>
     <row r="971" ht="15.75" customHeight="1">
-      <c r="B971" s="7"/>
+      <c r="A971" s="3">
+        <v>46261.0</v>
+      </c>
+      <c r="B971" s="6">
+        <v>2854.0</v>
+      </c>
     </row>
     <row r="972" ht="15.75" customHeight="1">
-      <c r="B972" s="7"/>
+      <c r="A972" s="3">
+        <v>46262.0</v>
+      </c>
+      <c r="B972" s="6">
+        <v>3032.0</v>
+      </c>
     </row>
     <row r="973" ht="15.75" customHeight="1">
-      <c r="B973" s="7"/>
+      <c r="A973" s="3">
+        <v>46263.0</v>
+      </c>
+      <c r="B973" s="6">
+        <v>3562.0</v>
+      </c>
     </row>
     <row r="974" ht="15.75" customHeight="1">
-      <c r="B974" s="7"/>
+      <c r="A974" s="3">
+        <v>46264.0</v>
+      </c>
+      <c r="B974" s="6">
+        <v>3743.0</v>
+      </c>
     </row>
     <row r="975" ht="15.75" customHeight="1">
-      <c r="B975" s="7"/>
+      <c r="A975" s="3">
+        <v>46265.0</v>
+      </c>
+      <c r="B975" s="6">
+        <v>2105.0</v>
+      </c>
     </row>
     <row r="976" ht="15.75" customHeight="1">
-      <c r="B976" s="7"/>
+      <c r="A976" s="3">
+        <v>46266.0</v>
+      </c>
+      <c r="B976" s="6">
+        <v>2201.0</v>
+      </c>
     </row>
     <row r="977" ht="15.75" customHeight="1">
-      <c r="B977" s="7"/>
+      <c r="A977" s="3">
+        <v>46267.0</v>
+      </c>
+      <c r="B977" s="6">
+        <v>2041.0</v>
+      </c>
     </row>
     <row r="978" ht="15.75" customHeight="1">
-      <c r="B978" s="7"/>
+      <c r="A978" s="3">
+        <v>46268.0</v>
+      </c>
+      <c r="B978" s="6">
+        <v>2299.0</v>
+      </c>
     </row>
     <row r="979" ht="15.75" customHeight="1">
-      <c r="B979" s="7"/>
+      <c r="A979" s="3">
+        <v>46269.0</v>
+      </c>
+      <c r="B979" s="6">
+        <v>3461.0</v>
+      </c>
     </row>
     <row r="980" ht="15.75" customHeight="1">
-      <c r="B980" s="7"/>
+      <c r="A980" s="3">
+        <v>46270.0</v>
+      </c>
+      <c r="B980" s="6">
+        <v>3790.0</v>
+      </c>
     </row>
     <row r="981" ht="15.75" customHeight="1">
-      <c r="B981" s="7"/>
+      <c r="A981" s="3">
+        <v>46271.0</v>
+      </c>
+      <c r="B981" s="6">
+        <v>3050.0</v>
+      </c>
     </row>
     <row r="982" ht="15.75" customHeight="1">
-      <c r="B982" s="7"/>
+      <c r="A982" s="3">
+        <v>46272.0</v>
+      </c>
+      <c r="B982" s="6">
+        <v>1659.0</v>
+      </c>
     </row>
     <row r="983" ht="15.75" customHeight="1">
-      <c r="B983" s="7"/>
+      <c r="A983" s="3">
+        <v>46273.0</v>
+      </c>
+      <c r="B983" s="6">
+        <v>1594.0</v>
+      </c>
     </row>
     <row r="984" ht="15.75" customHeight="1">
-      <c r="B984" s="7"/>
+      <c r="A984" s="3">
+        <v>46274.0</v>
+      </c>
+      <c r="B984" s="6">
+        <v>2057.0</v>
+      </c>
     </row>
     <row r="985" ht="15.75" customHeight="1">
-      <c r="B985" s="7"/>
+      <c r="A985" s="3">
+        <v>46275.0</v>
+      </c>
+      <c r="B985" s="6">
+        <v>3931.0</v>
+      </c>
     </row>
     <row r="986" ht="15.75" customHeight="1">
-      <c r="B986" s="7"/>
+      <c r="A986" s="3">
+        <v>46276.0</v>
+      </c>
+      <c r="B986" s="6">
+        <v>4351.0</v>
+      </c>
     </row>
     <row r="987" ht="15.75" customHeight="1">
-      <c r="B987" s="7"/>
+      <c r="A987" s="3">
+        <v>46277.0</v>
+      </c>
+      <c r="B987" s="6">
+        <v>3650.0</v>
+      </c>
     </row>
     <row r="988" ht="15.75" customHeight="1">
       <c r="B988" s="7"/>

--- a/venta.xlsx
+++ b/venta.xlsx
@@ -8208,33 +8208,71 @@
       </c>
     </row>
     <row r="988" ht="15.75" customHeight="1">
-      <c r="B988" s="7"/>
+      <c r="A988" s="3">
+        <v>46278.0</v>
+      </c>
+      <c r="B988" s="6">
+        <v>3114.0</v>
+      </c>
     </row>
     <row r="989" ht="15.75" customHeight="1">
-      <c r="B989" s="7"/>
+      <c r="A989" s="3">
+        <v>46279.0</v>
+      </c>
+      <c r="B989" s="6">
+        <v>1349.0</v>
+      </c>
     </row>
     <row r="990" ht="15.75" customHeight="1">
-      <c r="B990" s="7"/>
+      <c r="A990" s="3">
+        <v>46280.0</v>
+      </c>
+      <c r="B990" s="6">
+        <v>1245.0</v>
+      </c>
     </row>
     <row r="991" ht="15.75" customHeight="1">
-      <c r="B991" s="7"/>
+      <c r="A991" s="3">
+        <v>46281.0</v>
+      </c>
+      <c r="B991" s="6">
+        <v>1673.0</v>
+      </c>
     </row>
     <row r="992" ht="15.75" customHeight="1">
-      <c r="B992" s="7"/>
+      <c r="A992" s="3">
+        <v>46282.0</v>
+      </c>
+      <c r="B992" s="6">
+        <v>1789.0</v>
+      </c>
     </row>
     <row r="993" ht="15.75" customHeight="1">
-      <c r="B993" s="7"/>
+      <c r="A993" s="3">
+        <v>46283.0</v>
+      </c>
+      <c r="B993" s="6">
+        <v>3816.0</v>
+      </c>
     </row>
     <row r="994" ht="15.75" customHeight="1">
-      <c r="B994" s="7"/>
+      <c r="A994" s="3">
+        <v>46284.0</v>
+      </c>
+      <c r="B994" s="6">
+        <v>4819.0</v>
+      </c>
     </row>
     <row r="995" ht="15.75" customHeight="1">
+      <c r="A995" s="3"/>
       <c r="B995" s="7"/>
     </row>
     <row r="996" ht="15.75" customHeight="1">
+      <c r="A996" s="3"/>
       <c r="B996" s="7"/>
     </row>
     <row r="997" ht="15.75" customHeight="1">
+      <c r="A997" s="3"/>
       <c r="B997" s="7"/>
     </row>
     <row r="998" ht="15.75" customHeight="1">

--- a/venta.xlsx
+++ b/venta.xlsx
@@ -9,7 +9,7 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="ARRhuAjUEnGo0TOMX7OCRprFM1g7ehXUNhmaLzaxMB4="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="x/ey60bGMYdY79IbxddJAL3yRtLIndA7fnJRmsU2i/M="/>
     </ext>
   </extLst>
 </workbook>
@@ -8264,25 +8264,4112 @@
       </c>
     </row>
     <row r="995" ht="15.75" customHeight="1">
-      <c r="A995" s="3"/>
-      <c r="B995" s="7"/>
+      <c r="A995" s="3">
+        <v>46285.0</v>
+      </c>
+      <c r="B995" s="6">
+        <v>3012.97</v>
+      </c>
     </row>
     <row r="996" ht="15.75" customHeight="1">
-      <c r="A996" s="3"/>
-      <c r="B996" s="7"/>
+      <c r="A996" s="3">
+        <v>46286.0</v>
+      </c>
+      <c r="B996" s="6">
+        <v>1807.88</v>
+      </c>
     </row>
     <row r="997" ht="15.75" customHeight="1">
-      <c r="A997" s="3"/>
-      <c r="B997" s="7"/>
+      <c r="A997" s="3">
+        <v>46287.0</v>
+      </c>
+      <c r="B997" s="6">
+        <v>3515.93</v>
+      </c>
     </row>
     <row r="998" ht="15.75" customHeight="1">
-      <c r="B998" s="7"/>
+      <c r="A998" s="3">
+        <v>46288.0</v>
+      </c>
+      <c r="B998" s="6">
+        <v>3883.02</v>
+      </c>
     </row>
     <row r="999" ht="15.75" customHeight="1">
-      <c r="B999" s="7"/>
+      <c r="A999" s="3">
+        <v>46289.0</v>
+      </c>
+      <c r="B999" s="6">
+        <v>2126.91</v>
+      </c>
     </row>
     <row r="1000" ht="15.75" customHeight="1">
-      <c r="B1000" s="7"/>
+      <c r="A1000" s="3">
+        <v>46290.0</v>
+      </c>
+      <c r="B1000" s="6">
+        <v>3360.57</v>
+      </c>
+    </row>
+    <row r="1001" ht="15.75" customHeight="1">
+      <c r="A1001" s="3">
+        <v>46291.0</v>
+      </c>
+      <c r="B1001" s="6">
+        <v>3545.91</v>
+      </c>
+    </row>
+    <row r="1002" ht="15.75" customHeight="1">
+      <c r="A1002" s="3">
+        <v>46292.0</v>
+      </c>
+      <c r="B1002" s="6">
+        <v>2163.96</v>
+      </c>
+    </row>
+    <row r="1003" ht="15.75" customHeight="1">
+      <c r="A1003" s="3">
+        <v>46293.0</v>
+      </c>
+      <c r="B1003" s="6">
+        <v>1252.38</v>
+      </c>
+    </row>
+    <row r="1004" ht="15.75" customHeight="1">
+      <c r="A1004" s="3">
+        <v>46294.0</v>
+      </c>
+      <c r="B1004" s="6">
+        <v>1847.77</v>
+      </c>
+    </row>
+    <row r="1005" ht="15.75" customHeight="1">
+      <c r="A1005" s="3">
+        <v>46295.0</v>
+      </c>
+      <c r="B1005" s="6">
+        <v>1611.16</v>
+      </c>
+    </row>
+    <row r="1006" ht="15.75" customHeight="1">
+      <c r="A1006" s="3">
+        <v>46296.0</v>
+      </c>
+      <c r="B1006" s="6">
+        <v>2443.8</v>
+      </c>
+    </row>
+    <row r="1007" ht="15.75" customHeight="1">
+      <c r="A1007" s="3">
+        <v>46297.0</v>
+      </c>
+      <c r="B1007" s="6">
+        <v>3846.91</v>
+      </c>
+    </row>
+    <row r="1008" ht="15.75" customHeight="1">
+      <c r="A1008" s="3">
+        <v>46298.0</v>
+      </c>
+      <c r="B1008" s="6">
+        <v>3401.42</v>
+      </c>
+    </row>
+    <row r="1009" ht="15.75" customHeight="1">
+      <c r="A1009" s="3">
+        <v>46299.0</v>
+      </c>
+      <c r="B1009" s="6">
+        <v>3013.64</v>
+      </c>
+    </row>
+    <row r="1010" ht="15.75" customHeight="1">
+      <c r="A1010" s="3">
+        <v>46300.0</v>
+      </c>
+      <c r="B1010" s="6">
+        <v>1470.48</v>
+      </c>
+    </row>
+    <row r="1011" ht="15.75" customHeight="1">
+      <c r="A1011" s="3">
+        <v>46301.0</v>
+      </c>
+      <c r="B1011" s="6">
+        <v>1500.76</v>
+      </c>
+    </row>
+    <row r="1012" ht="15.75" customHeight="1">
+      <c r="A1012" s="3">
+        <v>46302.0</v>
+      </c>
+      <c r="B1012" s="6">
+        <v>1618.3</v>
+      </c>
+    </row>
+    <row r="1013" ht="15.75" customHeight="1">
+      <c r="A1013" s="3">
+        <v>46303.0</v>
+      </c>
+      <c r="B1013" s="6">
+        <v>1732.46</v>
+      </c>
+    </row>
+    <row r="1014" ht="15.75" customHeight="1">
+      <c r="A1014" s="3">
+        <v>46304.0</v>
+      </c>
+      <c r="B1014" s="6">
+        <v>3154.07</v>
+      </c>
+    </row>
+    <row r="1015" ht="15.75" customHeight="1">
+      <c r="A1015" s="3">
+        <v>46305.0</v>
+      </c>
+      <c r="B1015" s="6">
+        <v>3717.0</v>
+      </c>
+    </row>
+    <row r="1016" ht="15.75" customHeight="1">
+      <c r="A1016" s="3"/>
+      <c r="B1016" s="7"/>
+    </row>
+    <row r="1017" ht="15.75" customHeight="1">
+      <c r="A1017" s="3"/>
+      <c r="B1017" s="7"/>
+    </row>
+    <row r="1018" ht="15.75" customHeight="1">
+      <c r="A1018" s="3"/>
+      <c r="B1018" s="7"/>
+    </row>
+    <row r="1019" ht="15.75" customHeight="1">
+      <c r="A1019" s="3"/>
+      <c r="B1019" s="7"/>
+    </row>
+    <row r="1020" ht="15.75" customHeight="1">
+      <c r="A1020" s="3"/>
+      <c r="B1020" s="7"/>
+    </row>
+    <row r="1021" ht="15.75" customHeight="1">
+      <c r="A1021" s="3"/>
+      <c r="B1021" s="7"/>
+    </row>
+    <row r="1022" ht="15.75" customHeight="1">
+      <c r="A1022" s="3"/>
+      <c r="B1022" s="7"/>
+    </row>
+    <row r="1023" ht="15.75" customHeight="1">
+      <c r="A1023" s="3"/>
+      <c r="B1023" s="7"/>
+    </row>
+    <row r="1024" ht="15.75" customHeight="1">
+      <c r="A1024" s="3"/>
+      <c r="B1024" s="7"/>
+    </row>
+    <row r="1025" ht="15.75" customHeight="1">
+      <c r="A1025" s="3"/>
+      <c r="B1025" s="7"/>
+    </row>
+    <row r="1026" ht="15.75" customHeight="1">
+      <c r="A1026" s="3"/>
+      <c r="B1026" s="7"/>
+    </row>
+    <row r="1027" ht="15.75" customHeight="1">
+      <c r="A1027" s="3"/>
+      <c r="B1027" s="7"/>
+    </row>
+    <row r="1028" ht="15.75" customHeight="1">
+      <c r="A1028" s="3"/>
+      <c r="B1028" s="7"/>
+    </row>
+    <row r="1029" ht="15.75" customHeight="1">
+      <c r="A1029" s="3"/>
+      <c r="B1029" s="7"/>
+    </row>
+    <row r="1030" ht="15.75" customHeight="1">
+      <c r="A1030" s="3"/>
+      <c r="B1030" s="7"/>
+    </row>
+    <row r="1031" ht="15.75" customHeight="1">
+      <c r="A1031" s="3"/>
+      <c r="B1031" s="7"/>
+    </row>
+    <row r="1032" ht="15.75" customHeight="1">
+      <c r="A1032" s="3"/>
+      <c r="B1032" s="7"/>
+    </row>
+    <row r="1033" ht="15.75" customHeight="1">
+      <c r="A1033" s="3"/>
+      <c r="B1033" s="7"/>
+    </row>
+    <row r="1034" ht="15.75" customHeight="1">
+      <c r="A1034" s="3"/>
+      <c r="B1034" s="7"/>
+    </row>
+    <row r="1035" ht="15.75" customHeight="1">
+      <c r="A1035" s="3"/>
+      <c r="B1035" s="7"/>
+    </row>
+    <row r="1036" ht="15.75" customHeight="1">
+      <c r="A1036" s="3"/>
+      <c r="B1036" s="7"/>
+    </row>
+    <row r="1037" ht="15.75" customHeight="1">
+      <c r="A1037" s="3"/>
+      <c r="B1037" s="7"/>
+    </row>
+    <row r="1038" ht="15.75" customHeight="1">
+      <c r="A1038" s="3"/>
+      <c r="B1038" s="7"/>
+    </row>
+    <row r="1039" ht="15.75" customHeight="1">
+      <c r="A1039" s="3"/>
+      <c r="B1039" s="7"/>
+    </row>
+    <row r="1040" ht="15.75" customHeight="1">
+      <c r="A1040" s="3"/>
+      <c r="B1040" s="7"/>
+    </row>
+    <row r="1041" ht="15.75" customHeight="1">
+      <c r="A1041" s="3"/>
+      <c r="B1041" s="7"/>
+    </row>
+    <row r="1042" ht="15.75" customHeight="1">
+      <c r="A1042" s="3"/>
+      <c r="B1042" s="7"/>
+    </row>
+    <row r="1043" ht="15.75" customHeight="1">
+      <c r="A1043" s="3"/>
+      <c r="B1043" s="7"/>
+    </row>
+    <row r="1044" ht="15.75" customHeight="1">
+      <c r="A1044" s="3"/>
+      <c r="B1044" s="7"/>
+    </row>
+    <row r="1045" ht="15.75" customHeight="1">
+      <c r="A1045" s="3"/>
+      <c r="B1045" s="7"/>
+    </row>
+    <row r="1046" ht="15.75" customHeight="1">
+      <c r="A1046" s="3"/>
+      <c r="B1046" s="7"/>
+    </row>
+    <row r="1047" ht="15.75" customHeight="1">
+      <c r="A1047" s="3"/>
+      <c r="B1047" s="7"/>
+    </row>
+    <row r="1048" ht="15.75" customHeight="1">
+      <c r="A1048" s="3"/>
+      <c r="B1048" s="7"/>
+    </row>
+    <row r="1049" ht="15.75" customHeight="1">
+      <c r="A1049" s="3"/>
+      <c r="B1049" s="7"/>
+    </row>
+    <row r="1050" ht="15.75" customHeight="1">
+      <c r="A1050" s="3"/>
+      <c r="B1050" s="7"/>
+    </row>
+    <row r="1051" ht="15.75" customHeight="1">
+      <c r="A1051" s="3"/>
+      <c r="B1051" s="7"/>
+    </row>
+    <row r="1052" ht="15.75" customHeight="1">
+      <c r="A1052" s="3"/>
+      <c r="B1052" s="7"/>
+    </row>
+    <row r="1053" ht="15.75" customHeight="1">
+      <c r="A1053" s="3"/>
+      <c r="B1053" s="7"/>
+    </row>
+    <row r="1054" ht="15.75" customHeight="1">
+      <c r="A1054" s="3"/>
+      <c r="B1054" s="7"/>
+    </row>
+    <row r="1055" ht="15.75" customHeight="1">
+      <c r="A1055" s="3"/>
+      <c r="B1055" s="7"/>
+    </row>
+    <row r="1056" ht="15.75" customHeight="1">
+      <c r="A1056" s="3"/>
+      <c r="B1056" s="7"/>
+    </row>
+    <row r="1057" ht="15.75" customHeight="1">
+      <c r="A1057" s="3"/>
+      <c r="B1057" s="7"/>
+    </row>
+    <row r="1058" ht="15.75" customHeight="1">
+      <c r="A1058" s="3"/>
+      <c r="B1058" s="7"/>
+    </row>
+    <row r="1059" ht="15.75" customHeight="1">
+      <c r="A1059" s="3"/>
+      <c r="B1059" s="7"/>
+    </row>
+    <row r="1060" ht="15.75" customHeight="1">
+      <c r="A1060" s="3"/>
+      <c r="B1060" s="7"/>
+    </row>
+    <row r="1061" ht="15.75" customHeight="1">
+      <c r="A1061" s="3"/>
+      <c r="B1061" s="7"/>
+    </row>
+    <row r="1062" ht="15.75" customHeight="1">
+      <c r="A1062" s="3"/>
+      <c r="B1062" s="7"/>
+    </row>
+    <row r="1063" ht="15.75" customHeight="1">
+      <c r="A1063" s="3"/>
+      <c r="B1063" s="7"/>
+    </row>
+    <row r="1064" ht="15.75" customHeight="1">
+      <c r="A1064" s="3"/>
+      <c r="B1064" s="7"/>
+    </row>
+    <row r="1065" ht="15.75" customHeight="1">
+      <c r="A1065" s="3"/>
+      <c r="B1065" s="7"/>
+    </row>
+    <row r="1066" ht="15.75" customHeight="1">
+      <c r="A1066" s="3"/>
+      <c r="B1066" s="7"/>
+    </row>
+    <row r="1067" ht="15.75" customHeight="1">
+      <c r="A1067" s="3"/>
+      <c r="B1067" s="7"/>
+    </row>
+    <row r="1068" ht="15.75" customHeight="1">
+      <c r="A1068" s="3"/>
+      <c r="B1068" s="7"/>
+    </row>
+    <row r="1069" ht="15.75" customHeight="1">
+      <c r="A1069" s="3"/>
+      <c r="B1069" s="7"/>
+    </row>
+    <row r="1070" ht="15.75" customHeight="1">
+      <c r="A1070" s="3"/>
+      <c r="B1070" s="7"/>
+    </row>
+    <row r="1071" ht="15.75" customHeight="1">
+      <c r="A1071" s="3"/>
+      <c r="B1071" s="7"/>
+    </row>
+    <row r="1072" ht="15.75" customHeight="1">
+      <c r="A1072" s="3"/>
+      <c r="B1072" s="7"/>
+    </row>
+    <row r="1073" ht="15.75" customHeight="1">
+      <c r="A1073" s="3"/>
+      <c r="B1073" s="7"/>
+    </row>
+    <row r="1074" ht="15.75" customHeight="1">
+      <c r="A1074" s="3"/>
+      <c r="B1074" s="7"/>
+    </row>
+    <row r="1075" ht="15.75" customHeight="1">
+      <c r="A1075" s="3"/>
+      <c r="B1075" s="7"/>
+    </row>
+    <row r="1076" ht="15.75" customHeight="1">
+      <c r="A1076" s="3"/>
+      <c r="B1076" s="7"/>
+    </row>
+    <row r="1077" ht="15.75" customHeight="1">
+      <c r="A1077" s="3"/>
+      <c r="B1077" s="7"/>
+    </row>
+    <row r="1078" ht="15.75" customHeight="1">
+      <c r="A1078" s="3"/>
+      <c r="B1078" s="7"/>
+    </row>
+    <row r="1079" ht="15.75" customHeight="1">
+      <c r="A1079" s="3"/>
+      <c r="B1079" s="7"/>
+    </row>
+    <row r="1080" ht="15.75" customHeight="1">
+      <c r="A1080" s="3"/>
+      <c r="B1080" s="7"/>
+    </row>
+    <row r="1081" ht="15.75" customHeight="1">
+      <c r="A1081" s="3"/>
+      <c r="B1081" s="7"/>
+    </row>
+    <row r="1082" ht="15.75" customHeight="1">
+      <c r="A1082" s="3"/>
+      <c r="B1082" s="7"/>
+    </row>
+    <row r="1083" ht="15.75" customHeight="1">
+      <c r="A1083" s="3"/>
+      <c r="B1083" s="7"/>
+    </row>
+    <row r="1084" ht="15.75" customHeight="1">
+      <c r="A1084" s="3"/>
+      <c r="B1084" s="7"/>
+    </row>
+    <row r="1085" ht="15.75" customHeight="1">
+      <c r="A1085" s="3"/>
+      <c r="B1085" s="7"/>
+    </row>
+    <row r="1086" ht="15.75" customHeight="1">
+      <c r="A1086" s="3"/>
+      <c r="B1086" s="7"/>
+    </row>
+    <row r="1087" ht="15.75" customHeight="1">
+      <c r="A1087" s="3"/>
+      <c r="B1087" s="7"/>
+    </row>
+    <row r="1088" ht="15.75" customHeight="1">
+      <c r="A1088" s="3"/>
+      <c r="B1088" s="7"/>
+    </row>
+    <row r="1089" ht="15.75" customHeight="1">
+      <c r="A1089" s="3"/>
+      <c r="B1089" s="7"/>
+    </row>
+    <row r="1090" ht="15.75" customHeight="1">
+      <c r="A1090" s="3"/>
+      <c r="B1090" s="7"/>
+    </row>
+    <row r="1091" ht="15.75" customHeight="1">
+      <c r="A1091" s="3"/>
+      <c r="B1091" s="7"/>
+    </row>
+    <row r="1092" ht="15.75" customHeight="1">
+      <c r="A1092" s="3"/>
+      <c r="B1092" s="7"/>
+    </row>
+    <row r="1093" ht="15.75" customHeight="1">
+      <c r="A1093" s="3"/>
+      <c r="B1093" s="7"/>
+    </row>
+    <row r="1094" ht="15.75" customHeight="1">
+      <c r="A1094" s="3"/>
+      <c r="B1094" s="7"/>
+    </row>
+    <row r="1095" ht="15.75" customHeight="1">
+      <c r="A1095" s="3"/>
+      <c r="B1095" s="7"/>
+    </row>
+    <row r="1096" ht="15.75" customHeight="1">
+      <c r="A1096" s="3"/>
+      <c r="B1096" s="7"/>
+    </row>
+    <row r="1097" ht="15.75" customHeight="1">
+      <c r="A1097" s="3"/>
+      <c r="B1097" s="7"/>
+    </row>
+    <row r="1098" ht="15.75" customHeight="1">
+      <c r="A1098" s="3"/>
+      <c r="B1098" s="7"/>
+    </row>
+    <row r="1099" ht="15.75" customHeight="1">
+      <c r="A1099" s="3"/>
+      <c r="B1099" s="7"/>
+    </row>
+    <row r="1100" ht="15.75" customHeight="1">
+      <c r="A1100" s="3"/>
+      <c r="B1100" s="7"/>
+    </row>
+    <row r="1101" ht="15.75" customHeight="1">
+      <c r="A1101" s="3"/>
+      <c r="B1101" s="7"/>
+    </row>
+    <row r="1102" ht="15.75" customHeight="1">
+      <c r="A1102" s="3"/>
+      <c r="B1102" s="7"/>
+    </row>
+    <row r="1103" ht="15.75" customHeight="1">
+      <c r="A1103" s="3"/>
+      <c r="B1103" s="7"/>
+    </row>
+    <row r="1104" ht="15.75" customHeight="1">
+      <c r="A1104" s="3"/>
+      <c r="B1104" s="7"/>
+    </row>
+    <row r="1105" ht="15.75" customHeight="1">
+      <c r="A1105" s="3"/>
+      <c r="B1105" s="7"/>
+    </row>
+    <row r="1106" ht="15.75" customHeight="1">
+      <c r="A1106" s="3"/>
+      <c r="B1106" s="7"/>
+    </row>
+    <row r="1107" ht="15.75" customHeight="1">
+      <c r="A1107" s="3"/>
+      <c r="B1107" s="7"/>
+    </row>
+    <row r="1108" ht="15.75" customHeight="1">
+      <c r="A1108" s="3"/>
+      <c r="B1108" s="7"/>
+    </row>
+    <row r="1109" ht="15.75" customHeight="1">
+      <c r="A1109" s="3"/>
+      <c r="B1109" s="7"/>
+    </row>
+    <row r="1110" ht="15.75" customHeight="1">
+      <c r="A1110" s="3"/>
+      <c r="B1110" s="7"/>
+    </row>
+    <row r="1111" ht="15.75" customHeight="1">
+      <c r="A1111" s="3"/>
+      <c r="B1111" s="7"/>
+    </row>
+    <row r="1112" ht="15.75" customHeight="1">
+      <c r="A1112" s="3"/>
+      <c r="B1112" s="7"/>
+    </row>
+    <row r="1113" ht="15.75" customHeight="1">
+      <c r="A1113" s="3"/>
+      <c r="B1113" s="7"/>
+    </row>
+    <row r="1114" ht="15.75" customHeight="1">
+      <c r="A1114" s="3"/>
+      <c r="B1114" s="7"/>
+    </row>
+    <row r="1115" ht="15.75" customHeight="1">
+      <c r="A1115" s="3"/>
+      <c r="B1115" s="7"/>
+    </row>
+    <row r="1116" ht="15.75" customHeight="1">
+      <c r="A1116" s="3"/>
+      <c r="B1116" s="7"/>
+    </row>
+    <row r="1117" ht="15.75" customHeight="1">
+      <c r="A1117" s="3"/>
+      <c r="B1117" s="7"/>
+    </row>
+    <row r="1118" ht="15.75" customHeight="1">
+      <c r="A1118" s="3"/>
+      <c r="B1118" s="7"/>
+    </row>
+    <row r="1119" ht="15.75" customHeight="1">
+      <c r="A1119" s="3"/>
+      <c r="B1119" s="7"/>
+    </row>
+    <row r="1120" ht="15.75" customHeight="1">
+      <c r="A1120" s="3"/>
+      <c r="B1120" s="7"/>
+    </row>
+    <row r="1121" ht="15.75" customHeight="1">
+      <c r="A1121" s="3"/>
+      <c r="B1121" s="7"/>
+    </row>
+    <row r="1122" ht="15.75" customHeight="1">
+      <c r="A1122" s="3"/>
+      <c r="B1122" s="7"/>
+    </row>
+    <row r="1123" ht="15.75" customHeight="1">
+      <c r="A1123" s="3"/>
+      <c r="B1123" s="7"/>
+    </row>
+    <row r="1124" ht="15.75" customHeight="1">
+      <c r="A1124" s="3"/>
+      <c r="B1124" s="7"/>
+    </row>
+    <row r="1125" ht="15.75" customHeight="1">
+      <c r="A1125" s="3"/>
+      <c r="B1125" s="7"/>
+    </row>
+    <row r="1126" ht="15.75" customHeight="1">
+      <c r="A1126" s="3"/>
+      <c r="B1126" s="7"/>
+    </row>
+    <row r="1127" ht="15.75" customHeight="1">
+      <c r="A1127" s="3"/>
+      <c r="B1127" s="7"/>
+    </row>
+    <row r="1128" ht="15.75" customHeight="1">
+      <c r="A1128" s="3"/>
+      <c r="B1128" s="7"/>
+    </row>
+    <row r="1129" ht="15.75" customHeight="1">
+      <c r="A1129" s="3"/>
+      <c r="B1129" s="7"/>
+    </row>
+    <row r="1130" ht="15.75" customHeight="1">
+      <c r="A1130" s="3"/>
+      <c r="B1130" s="7"/>
+    </row>
+    <row r="1131" ht="15.75" customHeight="1">
+      <c r="A1131" s="3"/>
+      <c r="B1131" s="7"/>
+    </row>
+    <row r="1132" ht="15.75" customHeight="1">
+      <c r="A1132" s="3"/>
+      <c r="B1132" s="7"/>
+    </row>
+    <row r="1133" ht="15.75" customHeight="1">
+      <c r="A1133" s="3"/>
+      <c r="B1133" s="7"/>
+    </row>
+    <row r="1134" ht="15.75" customHeight="1">
+      <c r="A1134" s="3"/>
+      <c r="B1134" s="7"/>
+    </row>
+    <row r="1135" ht="15.75" customHeight="1">
+      <c r="A1135" s="3"/>
+      <c r="B1135" s="7"/>
+    </row>
+    <row r="1136" ht="15.75" customHeight="1">
+      <c r="A1136" s="3"/>
+      <c r="B1136" s="7"/>
+    </row>
+    <row r="1137" ht="15.75" customHeight="1">
+      <c r="A1137" s="3"/>
+      <c r="B1137" s="7"/>
+    </row>
+    <row r="1138" ht="15.75" customHeight="1">
+      <c r="A1138" s="3"/>
+      <c r="B1138" s="7"/>
+    </row>
+    <row r="1139" ht="15.75" customHeight="1">
+      <c r="A1139" s="3"/>
+      <c r="B1139" s="7"/>
+    </row>
+    <row r="1140" ht="15.75" customHeight="1">
+      <c r="A1140" s="3"/>
+      <c r="B1140" s="7"/>
+    </row>
+    <row r="1141" ht="15.75" customHeight="1">
+      <c r="A1141" s="3"/>
+      <c r="B1141" s="7"/>
+    </row>
+    <row r="1142" ht="15.75" customHeight="1">
+      <c r="A1142" s="3"/>
+      <c r="B1142" s="7"/>
+    </row>
+    <row r="1143" ht="15.75" customHeight="1">
+      <c r="A1143" s="3"/>
+      <c r="B1143" s="7"/>
+    </row>
+    <row r="1144" ht="15.75" customHeight="1">
+      <c r="A1144" s="3"/>
+      <c r="B1144" s="7"/>
+    </row>
+    <row r="1145" ht="15.75" customHeight="1">
+      <c r="A1145" s="3"/>
+      <c r="B1145" s="7"/>
+    </row>
+    <row r="1146" ht="15.75" customHeight="1">
+      <c r="A1146" s="3"/>
+      <c r="B1146" s="7"/>
+    </row>
+    <row r="1147" ht="15.75" customHeight="1">
+      <c r="A1147" s="3"/>
+      <c r="B1147" s="7"/>
+    </row>
+    <row r="1148" ht="15.75" customHeight="1">
+      <c r="A1148" s="3"/>
+      <c r="B1148" s="7"/>
+    </row>
+    <row r="1149" ht="15.75" customHeight="1">
+      <c r="A1149" s="3"/>
+      <c r="B1149" s="7"/>
+    </row>
+    <row r="1150" ht="15.75" customHeight="1">
+      <c r="A1150" s="3"/>
+      <c r="B1150" s="7"/>
+    </row>
+    <row r="1151" ht="15.75" customHeight="1">
+      <c r="A1151" s="3"/>
+      <c r="B1151" s="7"/>
+    </row>
+    <row r="1152" ht="15.75" customHeight="1">
+      <c r="A1152" s="3"/>
+      <c r="B1152" s="7"/>
+    </row>
+    <row r="1153" ht="15.75" customHeight="1">
+      <c r="A1153" s="3"/>
+      <c r="B1153" s="7"/>
+    </row>
+    <row r="1154" ht="15.75" customHeight="1">
+      <c r="A1154" s="3"/>
+      <c r="B1154" s="7"/>
+    </row>
+    <row r="1155" ht="15.75" customHeight="1">
+      <c r="A1155" s="3"/>
+      <c r="B1155" s="7"/>
+    </row>
+    <row r="1156" ht="15.75" customHeight="1">
+      <c r="A1156" s="3"/>
+      <c r="B1156" s="7"/>
+    </row>
+    <row r="1157" ht="15.75" customHeight="1">
+      <c r="A1157" s="3"/>
+      <c r="B1157" s="7"/>
+    </row>
+    <row r="1158" ht="15.75" customHeight="1">
+      <c r="A1158" s="3"/>
+      <c r="B1158" s="7"/>
+    </row>
+    <row r="1159" ht="15.75" customHeight="1">
+      <c r="A1159" s="3"/>
+      <c r="B1159" s="7"/>
+    </row>
+    <row r="1160" ht="15.75" customHeight="1">
+      <c r="A1160" s="3"/>
+      <c r="B1160" s="7"/>
+    </row>
+    <row r="1161" ht="15.75" customHeight="1">
+      <c r="A1161" s="3"/>
+      <c r="B1161" s="7"/>
+    </row>
+    <row r="1162" ht="15.75" customHeight="1">
+      <c r="A1162" s="3"/>
+      <c r="B1162" s="7"/>
+    </row>
+    <row r="1163" ht="15.75" customHeight="1">
+      <c r="A1163" s="3"/>
+      <c r="B1163" s="7"/>
+    </row>
+    <row r="1164" ht="15.75" customHeight="1">
+      <c r="A1164" s="3"/>
+      <c r="B1164" s="7"/>
+    </row>
+    <row r="1165" ht="15.75" customHeight="1">
+      <c r="A1165" s="3"/>
+      <c r="B1165" s="7"/>
+    </row>
+    <row r="1166" ht="15.75" customHeight="1">
+      <c r="A1166" s="3"/>
+      <c r="B1166" s="7"/>
+    </row>
+    <row r="1167" ht="15.75" customHeight="1">
+      <c r="A1167" s="3"/>
+      <c r="B1167" s="7"/>
+    </row>
+    <row r="1168" ht="15.75" customHeight="1">
+      <c r="A1168" s="3"/>
+      <c r="B1168" s="7"/>
+    </row>
+    <row r="1169" ht="15.75" customHeight="1">
+      <c r="A1169" s="3"/>
+      <c r="B1169" s="7"/>
+    </row>
+    <row r="1170" ht="15.75" customHeight="1">
+      <c r="A1170" s="3"/>
+      <c r="B1170" s="7"/>
+    </row>
+    <row r="1171" ht="15.75" customHeight="1">
+      <c r="A1171" s="3"/>
+      <c r="B1171" s="7"/>
+    </row>
+    <row r="1172" ht="15.75" customHeight="1">
+      <c r="A1172" s="3"/>
+      <c r="B1172" s="7"/>
+    </row>
+    <row r="1173" ht="15.75" customHeight="1">
+      <c r="A1173" s="3"/>
+      <c r="B1173" s="7"/>
+    </row>
+    <row r="1174" ht="15.75" customHeight="1">
+      <c r="A1174" s="3"/>
+      <c r="B1174" s="7"/>
+    </row>
+    <row r="1175" ht="15.75" customHeight="1">
+      <c r="A1175" s="3"/>
+      <c r="B1175" s="7"/>
+    </row>
+    <row r="1176" ht="15.75" customHeight="1">
+      <c r="A1176" s="3"/>
+      <c r="B1176" s="7"/>
+    </row>
+    <row r="1177" ht="15.75" customHeight="1">
+      <c r="A1177" s="3"/>
+      <c r="B1177" s="7"/>
+    </row>
+    <row r="1178" ht="15.75" customHeight="1">
+      <c r="A1178" s="3"/>
+      <c r="B1178" s="7"/>
+    </row>
+    <row r="1179" ht="15.75" customHeight="1">
+      <c r="A1179" s="3"/>
+      <c r="B1179" s="7"/>
+    </row>
+    <row r="1180" ht="15.75" customHeight="1">
+      <c r="A1180" s="3"/>
+      <c r="B1180" s="7"/>
+    </row>
+    <row r="1181" ht="15.75" customHeight="1">
+      <c r="A1181" s="3"/>
+      <c r="B1181" s="7"/>
+    </row>
+    <row r="1182" ht="15.75" customHeight="1">
+      <c r="A1182" s="3"/>
+      <c r="B1182" s="7"/>
+    </row>
+    <row r="1183" ht="15.75" customHeight="1">
+      <c r="A1183" s="3"/>
+      <c r="B1183" s="7"/>
+    </row>
+    <row r="1184" ht="15.75" customHeight="1">
+      <c r="A1184" s="3"/>
+      <c r="B1184" s="7"/>
+    </row>
+    <row r="1185" ht="15.75" customHeight="1">
+      <c r="A1185" s="3"/>
+      <c r="B1185" s="7"/>
+    </row>
+    <row r="1186" ht="15.75" customHeight="1">
+      <c r="A1186" s="3"/>
+      <c r="B1186" s="7"/>
+    </row>
+    <row r="1187" ht="15.75" customHeight="1">
+      <c r="A1187" s="3"/>
+      <c r="B1187" s="7"/>
+    </row>
+    <row r="1188" ht="15.75" customHeight="1">
+      <c r="A1188" s="3"/>
+      <c r="B1188" s="7"/>
+    </row>
+    <row r="1189" ht="15.75" customHeight="1">
+      <c r="A1189" s="3"/>
+      <c r="B1189" s="7"/>
+    </row>
+    <row r="1190" ht="15.75" customHeight="1">
+      <c r="A1190" s="3"/>
+      <c r="B1190" s="7"/>
+    </row>
+    <row r="1191" ht="15.75" customHeight="1">
+      <c r="A1191" s="3"/>
+      <c r="B1191" s="7"/>
+    </row>
+    <row r="1192" ht="15.75" customHeight="1">
+      <c r="A1192" s="3"/>
+      <c r="B1192" s="7"/>
+    </row>
+    <row r="1193" ht="15.75" customHeight="1">
+      <c r="A1193" s="3"/>
+      <c r="B1193" s="7"/>
+    </row>
+    <row r="1194" ht="15.75" customHeight="1">
+      <c r="A1194" s="3"/>
+      <c r="B1194" s="7"/>
+    </row>
+    <row r="1195" ht="15.75" customHeight="1">
+      <c r="A1195" s="3"/>
+      <c r="B1195" s="7"/>
+    </row>
+    <row r="1196" ht="15.75" customHeight="1">
+      <c r="A1196" s="3"/>
+      <c r="B1196" s="7"/>
+    </row>
+    <row r="1197" ht="15.75" customHeight="1">
+      <c r="A1197" s="3"/>
+      <c r="B1197" s="7"/>
+    </row>
+    <row r="1198" ht="15.75" customHeight="1">
+      <c r="A1198" s="3"/>
+      <c r="B1198" s="7"/>
+    </row>
+    <row r="1199" ht="15.75" customHeight="1">
+      <c r="A1199" s="3"/>
+      <c r="B1199" s="7"/>
+    </row>
+    <row r="1200" ht="15.75" customHeight="1">
+      <c r="A1200" s="3"/>
+      <c r="B1200" s="7"/>
+    </row>
+    <row r="1201" ht="15.75" customHeight="1">
+      <c r="A1201" s="3"/>
+      <c r="B1201" s="7"/>
+    </row>
+    <row r="1202" ht="15.75" customHeight="1">
+      <c r="A1202" s="3"/>
+      <c r="B1202" s="7"/>
+    </row>
+    <row r="1203" ht="15.75" customHeight="1">
+      <c r="A1203" s="3"/>
+      <c r="B1203" s="7"/>
+    </row>
+    <row r="1204" ht="15.75" customHeight="1">
+      <c r="A1204" s="3"/>
+      <c r="B1204" s="7"/>
+    </row>
+    <row r="1205" ht="15.75" customHeight="1">
+      <c r="A1205" s="3"/>
+      <c r="B1205" s="7"/>
+    </row>
+    <row r="1206" ht="15.75" customHeight="1">
+      <c r="A1206" s="3"/>
+      <c r="B1206" s="7"/>
+    </row>
+    <row r="1207" ht="15.75" customHeight="1">
+      <c r="A1207" s="3"/>
+      <c r="B1207" s="7"/>
+    </row>
+    <row r="1208" ht="15.75" customHeight="1">
+      <c r="A1208" s="3"/>
+      <c r="B1208" s="7"/>
+    </row>
+    <row r="1209" ht="15.75" customHeight="1">
+      <c r="A1209" s="3"/>
+      <c r="B1209" s="7"/>
+    </row>
+    <row r="1210" ht="15.75" customHeight="1">
+      <c r="A1210" s="3"/>
+      <c r="B1210" s="7"/>
+    </row>
+    <row r="1211" ht="15.75" customHeight="1">
+      <c r="A1211" s="3"/>
+      <c r="B1211" s="7"/>
+    </row>
+    <row r="1212" ht="15.75" customHeight="1">
+      <c r="A1212" s="3"/>
+      <c r="B1212" s="7"/>
+    </row>
+    <row r="1213" ht="15.75" customHeight="1">
+      <c r="A1213" s="3"/>
+      <c r="B1213" s="7"/>
+    </row>
+    <row r="1214" ht="15.75" customHeight="1">
+      <c r="A1214" s="3"/>
+      <c r="B1214" s="7"/>
+    </row>
+    <row r="1215" ht="15.75" customHeight="1">
+      <c r="A1215" s="3"/>
+      <c r="B1215" s="7"/>
+    </row>
+    <row r="1216" ht="15.75" customHeight="1">
+      <c r="A1216" s="3"/>
+      <c r="B1216" s="7"/>
+    </row>
+    <row r="1217" ht="15.75" customHeight="1">
+      <c r="A1217" s="3"/>
+      <c r="B1217" s="7"/>
+    </row>
+    <row r="1218" ht="15.75" customHeight="1">
+      <c r="A1218" s="3"/>
+      <c r="B1218" s="7"/>
+    </row>
+    <row r="1219" ht="15.75" customHeight="1">
+      <c r="A1219" s="3"/>
+      <c r="B1219" s="7"/>
+    </row>
+    <row r="1220" ht="15.75" customHeight="1">
+      <c r="A1220" s="3"/>
+      <c r="B1220" s="7"/>
+    </row>
+    <row r="1221" ht="15.75" customHeight="1">
+      <c r="A1221" s="3"/>
+      <c r="B1221" s="7"/>
+    </row>
+    <row r="1222" ht="15.75" customHeight="1">
+      <c r="A1222" s="3"/>
+      <c r="B1222" s="7"/>
+    </row>
+    <row r="1223" ht="15.75" customHeight="1">
+      <c r="A1223" s="3"/>
+      <c r="B1223" s="7"/>
+    </row>
+    <row r="1224" ht="15.75" customHeight="1">
+      <c r="A1224" s="3"/>
+      <c r="B1224" s="7"/>
+    </row>
+    <row r="1225" ht="15.75" customHeight="1">
+      <c r="A1225" s="3"/>
+      <c r="B1225" s="7"/>
+    </row>
+    <row r="1226" ht="15.75" customHeight="1">
+      <c r="A1226" s="3"/>
+      <c r="B1226" s="7"/>
+    </row>
+    <row r="1227" ht="15.75" customHeight="1">
+      <c r="A1227" s="3"/>
+      <c r="B1227" s="7"/>
+    </row>
+    <row r="1228" ht="15.75" customHeight="1">
+      <c r="A1228" s="3"/>
+      <c r="B1228" s="7"/>
+    </row>
+    <row r="1229" ht="15.75" customHeight="1">
+      <c r="A1229" s="3"/>
+      <c r="B1229" s="7"/>
+    </row>
+    <row r="1230" ht="15.75" customHeight="1">
+      <c r="A1230" s="3"/>
+      <c r="B1230" s="7"/>
+    </row>
+    <row r="1231" ht="15.75" customHeight="1">
+      <c r="A1231" s="3"/>
+      <c r="B1231" s="7"/>
+    </row>
+    <row r="1232" ht="15.75" customHeight="1">
+      <c r="A1232" s="3"/>
+      <c r="B1232" s="7"/>
+    </row>
+    <row r="1233" ht="15.75" customHeight="1">
+      <c r="A1233" s="3"/>
+      <c r="B1233" s="7"/>
+    </row>
+    <row r="1234" ht="15.75" customHeight="1">
+      <c r="A1234" s="3"/>
+      <c r="B1234" s="7"/>
+    </row>
+    <row r="1235" ht="15.75" customHeight="1">
+      <c r="A1235" s="3"/>
+      <c r="B1235" s="7"/>
+    </row>
+    <row r="1236" ht="15.75" customHeight="1">
+      <c r="A1236" s="3"/>
+      <c r="B1236" s="7"/>
+    </row>
+    <row r="1237" ht="15.75" customHeight="1">
+      <c r="A1237" s="3"/>
+      <c r="B1237" s="7"/>
+    </row>
+    <row r="1238" ht="15.75" customHeight="1">
+      <c r="A1238" s="3"/>
+      <c r="B1238" s="7"/>
+    </row>
+    <row r="1239" ht="15.75" customHeight="1">
+      <c r="A1239" s="3"/>
+      <c r="B1239" s="7"/>
+    </row>
+    <row r="1240" ht="15.75" customHeight="1">
+      <c r="A1240" s="3"/>
+      <c r="B1240" s="7"/>
+    </row>
+    <row r="1241" ht="15.75" customHeight="1">
+      <c r="A1241" s="3"/>
+      <c r="B1241" s="7"/>
+    </row>
+    <row r="1242" ht="15.75" customHeight="1">
+      <c r="A1242" s="3"/>
+      <c r="B1242" s="7"/>
+    </row>
+    <row r="1243" ht="15.75" customHeight="1">
+      <c r="A1243" s="3"/>
+      <c r="B1243" s="7"/>
+    </row>
+    <row r="1244" ht="15.75" customHeight="1">
+      <c r="A1244" s="3"/>
+      <c r="B1244" s="7"/>
+    </row>
+    <row r="1245" ht="15.75" customHeight="1">
+      <c r="A1245" s="3"/>
+      <c r="B1245" s="7"/>
+    </row>
+    <row r="1246" ht="15.75" customHeight="1">
+      <c r="A1246" s="3"/>
+      <c r="B1246" s="7"/>
+    </row>
+    <row r="1247" ht="15.75" customHeight="1">
+      <c r="A1247" s="3"/>
+      <c r="B1247" s="7"/>
+    </row>
+    <row r="1248" ht="15.75" customHeight="1">
+      <c r="A1248" s="3"/>
+      <c r="B1248" s="7"/>
+    </row>
+    <row r="1249" ht="15.75" customHeight="1">
+      <c r="A1249" s="3"/>
+      <c r="B1249" s="7"/>
+    </row>
+    <row r="1250" ht="15.75" customHeight="1">
+      <c r="A1250" s="3"/>
+      <c r="B1250" s="7"/>
+    </row>
+    <row r="1251" ht="15.75" customHeight="1">
+      <c r="A1251" s="3"/>
+      <c r="B1251" s="7"/>
+    </row>
+    <row r="1252" ht="15.75" customHeight="1">
+      <c r="A1252" s="3"/>
+      <c r="B1252" s="7"/>
+    </row>
+    <row r="1253" ht="15.75" customHeight="1">
+      <c r="A1253" s="3"/>
+      <c r="B1253" s="7"/>
+    </row>
+    <row r="1254" ht="15.75" customHeight="1">
+      <c r="A1254" s="3"/>
+      <c r="B1254" s="7"/>
+    </row>
+    <row r="1255" ht="15.75" customHeight="1">
+      <c r="A1255" s="3"/>
+      <c r="B1255" s="7"/>
+    </row>
+    <row r="1256" ht="15.75" customHeight="1">
+      <c r="A1256" s="3"/>
+      <c r="B1256" s="7"/>
+    </row>
+    <row r="1257" ht="15.75" customHeight="1">
+      <c r="A1257" s="3"/>
+      <c r="B1257" s="7"/>
+    </row>
+    <row r="1258" ht="15.75" customHeight="1">
+      <c r="A1258" s="3"/>
+      <c r="B1258" s="7"/>
+    </row>
+    <row r="1259" ht="15.75" customHeight="1">
+      <c r="A1259" s="3"/>
+      <c r="B1259" s="7"/>
+    </row>
+    <row r="1260" ht="15.75" customHeight="1">
+      <c r="A1260" s="3"/>
+      <c r="B1260" s="7"/>
+    </row>
+    <row r="1261" ht="15.75" customHeight="1">
+      <c r="A1261" s="3"/>
+      <c r="B1261" s="7"/>
+    </row>
+    <row r="1262" ht="15.75" customHeight="1">
+      <c r="A1262" s="3"/>
+      <c r="B1262" s="7"/>
+    </row>
+    <row r="1263" ht="15.75" customHeight="1">
+      <c r="A1263" s="3"/>
+      <c r="B1263" s="7"/>
+    </row>
+    <row r="1264" ht="15.75" customHeight="1">
+      <c r="A1264" s="3"/>
+      <c r="B1264" s="7"/>
+    </row>
+    <row r="1265" ht="15.75" customHeight="1">
+      <c r="A1265" s="3"/>
+      <c r="B1265" s="7"/>
+    </row>
+    <row r="1266" ht="15.75" customHeight="1">
+      <c r="A1266" s="3"/>
+      <c r="B1266" s="7"/>
+    </row>
+    <row r="1267" ht="15.75" customHeight="1">
+      <c r="A1267" s="3"/>
+      <c r="B1267" s="7"/>
+    </row>
+    <row r="1268" ht="15.75" customHeight="1">
+      <c r="A1268" s="3"/>
+      <c r="B1268" s="7"/>
+    </row>
+    <row r="1269" ht="15.75" customHeight="1">
+      <c r="A1269" s="3"/>
+      <c r="B1269" s="7"/>
+    </row>
+    <row r="1270" ht="15.75" customHeight="1">
+      <c r="A1270" s="3"/>
+      <c r="B1270" s="7"/>
+    </row>
+    <row r="1271" ht="15.75" customHeight="1">
+      <c r="A1271" s="3"/>
+      <c r="B1271" s="7"/>
+    </row>
+    <row r="1272" ht="15.75" customHeight="1">
+      <c r="A1272" s="3"/>
+      <c r="B1272" s="7"/>
+    </row>
+    <row r="1273" ht="15.75" customHeight="1">
+      <c r="A1273" s="3"/>
+      <c r="B1273" s="7"/>
+    </row>
+    <row r="1274" ht="15.75" customHeight="1">
+      <c r="A1274" s="3"/>
+      <c r="B1274" s="7"/>
+    </row>
+    <row r="1275" ht="15.75" customHeight="1">
+      <c r="A1275" s="3"/>
+      <c r="B1275" s="7"/>
+    </row>
+    <row r="1276" ht="15.75" customHeight="1">
+      <c r="A1276" s="3"/>
+      <c r="B1276" s="7"/>
+    </row>
+    <row r="1277" ht="15.75" customHeight="1">
+      <c r="A1277" s="3"/>
+      <c r="B1277" s="7"/>
+    </row>
+    <row r="1278" ht="15.75" customHeight="1">
+      <c r="A1278" s="3"/>
+      <c r="B1278" s="7"/>
+    </row>
+    <row r="1279" ht="15.75" customHeight="1">
+      <c r="A1279" s="3"/>
+      <c r="B1279" s="7"/>
+    </row>
+    <row r="1280" ht="15.75" customHeight="1">
+      <c r="A1280" s="3"/>
+      <c r="B1280" s="7"/>
+    </row>
+    <row r="1281" ht="15.75" customHeight="1">
+      <c r="A1281" s="3"/>
+      <c r="B1281" s="7"/>
+    </row>
+    <row r="1282" ht="15.75" customHeight="1">
+      <c r="A1282" s="3"/>
+      <c r="B1282" s="7"/>
+    </row>
+    <row r="1283" ht="15.75" customHeight="1">
+      <c r="A1283" s="3"/>
+      <c r="B1283" s="7"/>
+    </row>
+    <row r="1284" ht="15.75" customHeight="1">
+      <c r="A1284" s="3"/>
+      <c r="B1284" s="7"/>
+    </row>
+    <row r="1285" ht="15.75" customHeight="1">
+      <c r="A1285" s="3"/>
+      <c r="B1285" s="7"/>
+    </row>
+    <row r="1286" ht="15.75" customHeight="1">
+      <c r="A1286" s="3"/>
+      <c r="B1286" s="7"/>
+    </row>
+    <row r="1287" ht="15.75" customHeight="1">
+      <c r="A1287" s="3"/>
+      <c r="B1287" s="7"/>
+    </row>
+    <row r="1288" ht="15.75" customHeight="1">
+      <c r="A1288" s="3"/>
+      <c r="B1288" s="7"/>
+    </row>
+    <row r="1289" ht="15.75" customHeight="1">
+      <c r="A1289" s="3"/>
+      <c r="B1289" s="7"/>
+    </row>
+    <row r="1290" ht="15.75" customHeight="1">
+      <c r="A1290" s="3"/>
+      <c r="B1290" s="7"/>
+    </row>
+    <row r="1291" ht="15.75" customHeight="1">
+      <c r="A1291" s="3"/>
+      <c r="B1291" s="7"/>
+    </row>
+    <row r="1292" ht="15.75" customHeight="1">
+      <c r="A1292" s="3"/>
+      <c r="B1292" s="7"/>
+    </row>
+    <row r="1293" ht="15.75" customHeight="1">
+      <c r="A1293" s="3"/>
+      <c r="B1293" s="7"/>
+    </row>
+    <row r="1294" ht="15.75" customHeight="1">
+      <c r="A1294" s="3"/>
+      <c r="B1294" s="7"/>
+    </row>
+    <row r="1295" ht="15.75" customHeight="1">
+      <c r="A1295" s="3"/>
+      <c r="B1295" s="7"/>
+    </row>
+    <row r="1296" ht="15.75" customHeight="1">
+      <c r="A1296" s="3"/>
+      <c r="B1296" s="7"/>
+    </row>
+    <row r="1297" ht="15.75" customHeight="1">
+      <c r="A1297" s="3"/>
+      <c r="B1297" s="7"/>
+    </row>
+    <row r="1298" ht="15.75" customHeight="1">
+      <c r="A1298" s="3"/>
+      <c r="B1298" s="7"/>
+    </row>
+    <row r="1299" ht="15.75" customHeight="1">
+      <c r="A1299" s="3"/>
+      <c r="B1299" s="7"/>
+    </row>
+    <row r="1300" ht="15.75" customHeight="1">
+      <c r="A1300" s="3"/>
+      <c r="B1300" s="7"/>
+    </row>
+    <row r="1301" ht="15.75" customHeight="1">
+      <c r="A1301" s="3"/>
+      <c r="B1301" s="7"/>
+    </row>
+    <row r="1302" ht="15.75" customHeight="1">
+      <c r="A1302" s="3"/>
+      <c r="B1302" s="7"/>
+    </row>
+    <row r="1303" ht="15.75" customHeight="1">
+      <c r="A1303" s="3"/>
+      <c r="B1303" s="7"/>
+    </row>
+    <row r="1304" ht="15.75" customHeight="1">
+      <c r="A1304" s="3"/>
+      <c r="B1304" s="7"/>
+    </row>
+    <row r="1305" ht="15.75" customHeight="1">
+      <c r="A1305" s="3"/>
+      <c r="B1305" s="7"/>
+    </row>
+    <row r="1306" ht="15.75" customHeight="1">
+      <c r="A1306" s="3"/>
+      <c r="B1306" s="7"/>
+    </row>
+    <row r="1307" ht="15.75" customHeight="1">
+      <c r="A1307" s="3"/>
+      <c r="B1307" s="7"/>
+    </row>
+    <row r="1308" ht="15.75" customHeight="1">
+      <c r="A1308" s="3"/>
+      <c r="B1308" s="7"/>
+    </row>
+    <row r="1309" ht="15.75" customHeight="1">
+      <c r="A1309" s="3"/>
+      <c r="B1309" s="7"/>
+    </row>
+    <row r="1310" ht="15.75" customHeight="1">
+      <c r="A1310" s="3"/>
+      <c r="B1310" s="7"/>
+    </row>
+    <row r="1311" ht="15.75" customHeight="1">
+      <c r="A1311" s="3"/>
+      <c r="B1311" s="7"/>
+    </row>
+    <row r="1312" ht="15.75" customHeight="1">
+      <c r="A1312" s="3"/>
+      <c r="B1312" s="7"/>
+    </row>
+    <row r="1313" ht="15.75" customHeight="1">
+      <c r="A1313" s="3"/>
+      <c r="B1313" s="7"/>
+    </row>
+    <row r="1314" ht="15.75" customHeight="1">
+      <c r="A1314" s="3"/>
+      <c r="B1314" s="7"/>
+    </row>
+    <row r="1315" ht="15.75" customHeight="1">
+      <c r="A1315" s="3"/>
+      <c r="B1315" s="7"/>
+    </row>
+    <row r="1316" ht="15.75" customHeight="1">
+      <c r="A1316" s="3"/>
+      <c r="B1316" s="7"/>
+    </row>
+    <row r="1317" ht="15.75" customHeight="1">
+      <c r="A1317" s="3"/>
+      <c r="B1317" s="7"/>
+    </row>
+    <row r="1318" ht="15.75" customHeight="1">
+      <c r="A1318" s="3"/>
+      <c r="B1318" s="7"/>
+    </row>
+    <row r="1319" ht="15.75" customHeight="1">
+      <c r="A1319" s="3"/>
+      <c r="B1319" s="7"/>
+    </row>
+    <row r="1320" ht="15.75" customHeight="1">
+      <c r="A1320" s="3"/>
+      <c r="B1320" s="7"/>
+    </row>
+    <row r="1321" ht="15.75" customHeight="1">
+      <c r="A1321" s="3"/>
+      <c r="B1321" s="7"/>
+    </row>
+    <row r="1322" ht="15.75" customHeight="1">
+      <c r="A1322" s="3"/>
+      <c r="B1322" s="7"/>
+    </row>
+    <row r="1323" ht="15.75" customHeight="1">
+      <c r="A1323" s="3"/>
+      <c r="B1323" s="7"/>
+    </row>
+    <row r="1324" ht="15.75" customHeight="1">
+      <c r="A1324" s="3"/>
+      <c r="B1324" s="7"/>
+    </row>
+    <row r="1325" ht="15.75" customHeight="1">
+      <c r="A1325" s="3"/>
+      <c r="B1325" s="7"/>
+    </row>
+    <row r="1326" ht="15.75" customHeight="1">
+      <c r="A1326" s="3"/>
+      <c r="B1326" s="7"/>
+    </row>
+    <row r="1327" ht="15.75" customHeight="1">
+      <c r="A1327" s="3"/>
+      <c r="B1327" s="7"/>
+    </row>
+    <row r="1328" ht="15.75" customHeight="1">
+      <c r="A1328" s="3"/>
+      <c r="B1328" s="7"/>
+    </row>
+    <row r="1329" ht="15.75" customHeight="1">
+      <c r="A1329" s="3"/>
+      <c r="B1329" s="7"/>
+    </row>
+    <row r="1330" ht="15.75" customHeight="1">
+      <c r="A1330" s="3"/>
+      <c r="B1330" s="7"/>
+    </row>
+    <row r="1331" ht="15.75" customHeight="1">
+      <c r="A1331" s="3"/>
+      <c r="B1331" s="7"/>
+    </row>
+    <row r="1332" ht="15.75" customHeight="1">
+      <c r="A1332" s="3"/>
+      <c r="B1332" s="7"/>
+    </row>
+    <row r="1333" ht="15.75" customHeight="1">
+      <c r="A1333" s="3"/>
+      <c r="B1333" s="7"/>
+    </row>
+    <row r="1334" ht="15.75" customHeight="1">
+      <c r="A1334" s="3"/>
+      <c r="B1334" s="7"/>
+    </row>
+    <row r="1335" ht="15.75" customHeight="1">
+      <c r="A1335" s="3"/>
+      <c r="B1335" s="7"/>
+    </row>
+    <row r="1336" ht="15.75" customHeight="1">
+      <c r="A1336" s="3"/>
+      <c r="B1336" s="7"/>
+    </row>
+    <row r="1337" ht="15.75" customHeight="1">
+      <c r="A1337" s="3"/>
+      <c r="B1337" s="7"/>
+    </row>
+    <row r="1338" ht="15.75" customHeight="1">
+      <c r="A1338" s="3"/>
+      <c r="B1338" s="7"/>
+    </row>
+    <row r="1339" ht="15.75" customHeight="1">
+      <c r="A1339" s="3"/>
+      <c r="B1339" s="7"/>
+    </row>
+    <row r="1340" ht="15.75" customHeight="1">
+      <c r="A1340" s="3"/>
+      <c r="B1340" s="7"/>
+    </row>
+    <row r="1341" ht="15.75" customHeight="1">
+      <c r="A1341" s="3"/>
+      <c r="B1341" s="7"/>
+    </row>
+    <row r="1342" ht="15.75" customHeight="1">
+      <c r="A1342" s="3"/>
+      <c r="B1342" s="7"/>
+    </row>
+    <row r="1343" ht="15.75" customHeight="1">
+      <c r="A1343" s="3"/>
+      <c r="B1343" s="7"/>
+    </row>
+    <row r="1344" ht="15.75" customHeight="1">
+      <c r="A1344" s="3"/>
+      <c r="B1344" s="7"/>
+    </row>
+    <row r="1345" ht="15.75" customHeight="1">
+      <c r="A1345" s="3"/>
+      <c r="B1345" s="7"/>
+    </row>
+    <row r="1346" ht="15.75" customHeight="1">
+      <c r="A1346" s="3"/>
+      <c r="B1346" s="7"/>
+    </row>
+    <row r="1347" ht="15.75" customHeight="1">
+      <c r="A1347" s="3"/>
+      <c r="B1347" s="7"/>
+    </row>
+    <row r="1348" ht="15.75" customHeight="1">
+      <c r="A1348" s="3"/>
+      <c r="B1348" s="7"/>
+    </row>
+    <row r="1349" ht="15.75" customHeight="1">
+      <c r="A1349" s="3"/>
+      <c r="B1349" s="7"/>
+    </row>
+    <row r="1350" ht="15.75" customHeight="1">
+      <c r="A1350" s="3"/>
+      <c r="B1350" s="7"/>
+    </row>
+    <row r="1351" ht="15.75" customHeight="1">
+      <c r="A1351" s="3"/>
+      <c r="B1351" s="7"/>
+    </row>
+    <row r="1352" ht="15.75" customHeight="1">
+      <c r="A1352" s="3"/>
+      <c r="B1352" s="7"/>
+    </row>
+    <row r="1353" ht="15.75" customHeight="1">
+      <c r="A1353" s="3"/>
+      <c r="B1353" s="7"/>
+    </row>
+    <row r="1354" ht="15.75" customHeight="1">
+      <c r="A1354" s="3"/>
+      <c r="B1354" s="7"/>
+    </row>
+    <row r="1355" ht="15.75" customHeight="1">
+      <c r="A1355" s="3"/>
+      <c r="B1355" s="7"/>
+    </row>
+    <row r="1356" ht="15.75" customHeight="1">
+      <c r="A1356" s="3"/>
+      <c r="B1356" s="7"/>
+    </row>
+    <row r="1357" ht="15.75" customHeight="1">
+      <c r="A1357" s="3"/>
+      <c r="B1357" s="7"/>
+    </row>
+    <row r="1358" ht="15.75" customHeight="1">
+      <c r="A1358" s="3"/>
+      <c r="B1358" s="7"/>
+    </row>
+    <row r="1359" ht="15.75" customHeight="1">
+      <c r="A1359" s="3"/>
+      <c r="B1359" s="7"/>
+    </row>
+    <row r="1360" ht="15.75" customHeight="1">
+      <c r="A1360" s="3"/>
+      <c r="B1360" s="7"/>
+    </row>
+    <row r="1361" ht="15.75" customHeight="1">
+      <c r="A1361" s="3"/>
+      <c r="B1361" s="7"/>
+    </row>
+    <row r="1362" ht="15.75" customHeight="1">
+      <c r="A1362" s="3"/>
+      <c r="B1362" s="7"/>
+    </row>
+    <row r="1363" ht="15.75" customHeight="1">
+      <c r="A1363" s="3"/>
+      <c r="B1363" s="7"/>
+    </row>
+    <row r="1364" ht="15.75" customHeight="1">
+      <c r="A1364" s="3"/>
+      <c r="B1364" s="7"/>
+    </row>
+    <row r="1365" ht="15.75" customHeight="1">
+      <c r="A1365" s="3"/>
+      <c r="B1365" s="7"/>
+    </row>
+    <row r="1366" ht="15.75" customHeight="1">
+      <c r="A1366" s="3"/>
+      <c r="B1366" s="7"/>
+    </row>
+    <row r="1367" ht="15.75" customHeight="1">
+      <c r="A1367" s="3"/>
+      <c r="B1367" s="7"/>
+    </row>
+    <row r="1368" ht="15.75" customHeight="1">
+      <c r="A1368" s="3"/>
+      <c r="B1368" s="7"/>
+    </row>
+    <row r="1369" ht="15.75" customHeight="1">
+      <c r="A1369" s="3"/>
+      <c r="B1369" s="7"/>
+    </row>
+    <row r="1370" ht="15.75" customHeight="1">
+      <c r="A1370" s="3"/>
+      <c r="B1370" s="7"/>
+    </row>
+    <row r="1371" ht="15.75" customHeight="1">
+      <c r="A1371" s="3"/>
+      <c r="B1371" s="7"/>
+    </row>
+    <row r="1372" ht="15.75" customHeight="1">
+      <c r="A1372" s="3"/>
+      <c r="B1372" s="7"/>
+    </row>
+    <row r="1373" ht="15.75" customHeight="1">
+      <c r="A1373" s="3"/>
+      <c r="B1373" s="7"/>
+    </row>
+    <row r="1374" ht="15.75" customHeight="1">
+      <c r="A1374" s="3"/>
+      <c r="B1374" s="7"/>
+    </row>
+    <row r="1375" ht="15.75" customHeight="1">
+      <c r="A1375" s="3"/>
+      <c r="B1375" s="7"/>
+    </row>
+    <row r="1376" ht="15.75" customHeight="1">
+      <c r="A1376" s="3"/>
+      <c r="B1376" s="7"/>
+    </row>
+    <row r="1377" ht="15.75" customHeight="1">
+      <c r="A1377" s="3"/>
+      <c r="B1377" s="7"/>
+    </row>
+    <row r="1378" ht="15.75" customHeight="1">
+      <c r="A1378" s="3"/>
+      <c r="B1378" s="7"/>
+    </row>
+    <row r="1379" ht="15.75" customHeight="1">
+      <c r="A1379" s="3"/>
+      <c r="B1379" s="7"/>
+    </row>
+    <row r="1380" ht="15.75" customHeight="1">
+      <c r="A1380" s="3"/>
+      <c r="B1380" s="7"/>
+    </row>
+    <row r="1381" ht="15.75" customHeight="1">
+      <c r="A1381" s="3"/>
+      <c r="B1381" s="7"/>
+    </row>
+    <row r="1382" ht="15.75" customHeight="1">
+      <c r="A1382" s="3"/>
+      <c r="B1382" s="7"/>
+    </row>
+    <row r="1383" ht="15.75" customHeight="1">
+      <c r="A1383" s="3"/>
+      <c r="B1383" s="7"/>
+    </row>
+    <row r="1384" ht="15.75" customHeight="1">
+      <c r="A1384" s="3"/>
+      <c r="B1384" s="7"/>
+    </row>
+    <row r="1385" ht="15.75" customHeight="1">
+      <c r="A1385" s="3"/>
+      <c r="B1385" s="7"/>
+    </row>
+    <row r="1386" ht="15.75" customHeight="1">
+      <c r="A1386" s="3"/>
+      <c r="B1386" s="7"/>
+    </row>
+    <row r="1387" ht="15.75" customHeight="1">
+      <c r="A1387" s="3"/>
+      <c r="B1387" s="7"/>
+    </row>
+    <row r="1388" ht="15.75" customHeight="1">
+      <c r="A1388" s="3"/>
+      <c r="B1388" s="7"/>
+    </row>
+    <row r="1389" ht="15.75" customHeight="1">
+      <c r="A1389" s="3"/>
+      <c r="B1389" s="7"/>
+    </row>
+    <row r="1390" ht="15.75" customHeight="1">
+      <c r="A1390" s="3"/>
+      <c r="B1390" s="7"/>
+    </row>
+    <row r="1391" ht="15.75" customHeight="1">
+      <c r="A1391" s="3"/>
+      <c r="B1391" s="7"/>
+    </row>
+    <row r="1392" ht="15.75" customHeight="1">
+      <c r="A1392" s="3"/>
+      <c r="B1392" s="7"/>
+    </row>
+    <row r="1393" ht="15.75" customHeight="1">
+      <c r="A1393" s="3"/>
+      <c r="B1393" s="7"/>
+    </row>
+    <row r="1394" ht="15.75" customHeight="1">
+      <c r="A1394" s="3"/>
+      <c r="B1394" s="7"/>
+    </row>
+    <row r="1395" ht="15.75" customHeight="1">
+      <c r="A1395" s="3"/>
+      <c r="B1395" s="7"/>
+    </row>
+    <row r="1396" ht="15.75" customHeight="1">
+      <c r="A1396" s="3"/>
+      <c r="B1396" s="7"/>
+    </row>
+    <row r="1397" ht="15.75" customHeight="1">
+      <c r="A1397" s="3"/>
+      <c r="B1397" s="7"/>
+    </row>
+    <row r="1398" ht="15.75" customHeight="1">
+      <c r="A1398" s="3"/>
+      <c r="B1398" s="7"/>
+    </row>
+    <row r="1399" ht="15.75" customHeight="1">
+      <c r="A1399" s="3"/>
+      <c r="B1399" s="7"/>
+    </row>
+    <row r="1400" ht="15.75" customHeight="1">
+      <c r="A1400" s="3"/>
+      <c r="B1400" s="7"/>
+    </row>
+    <row r="1401" ht="15.75" customHeight="1">
+      <c r="A1401" s="3"/>
+      <c r="B1401" s="7"/>
+    </row>
+    <row r="1402" ht="15.75" customHeight="1">
+      <c r="A1402" s="3"/>
+      <c r="B1402" s="7"/>
+    </row>
+    <row r="1403" ht="15.75" customHeight="1">
+      <c r="A1403" s="3"/>
+      <c r="B1403" s="7"/>
+    </row>
+    <row r="1404" ht="15.75" customHeight="1">
+      <c r="A1404" s="3"/>
+      <c r="B1404" s="7"/>
+    </row>
+    <row r="1405" ht="15.75" customHeight="1">
+      <c r="A1405" s="3"/>
+      <c r="B1405" s="7"/>
+    </row>
+    <row r="1406" ht="15.75" customHeight="1">
+      <c r="A1406" s="3"/>
+      <c r="B1406" s="7"/>
+    </row>
+    <row r="1407" ht="15.75" customHeight="1">
+      <c r="A1407" s="3"/>
+      <c r="B1407" s="7"/>
+    </row>
+    <row r="1408" ht="15.75" customHeight="1">
+      <c r="A1408" s="3"/>
+      <c r="B1408" s="7"/>
+    </row>
+    <row r="1409" ht="15.75" customHeight="1">
+      <c r="A1409" s="3"/>
+      <c r="B1409" s="7"/>
+    </row>
+    <row r="1410" ht="15.75" customHeight="1">
+      <c r="A1410" s="3"/>
+      <c r="B1410" s="7"/>
+    </row>
+    <row r="1411" ht="15.75" customHeight="1">
+      <c r="A1411" s="3"/>
+      <c r="B1411" s="7"/>
+    </row>
+    <row r="1412" ht="15.75" customHeight="1">
+      <c r="A1412" s="3"/>
+      <c r="B1412" s="7"/>
+    </row>
+    <row r="1413" ht="15.75" customHeight="1">
+      <c r="A1413" s="3"/>
+      <c r="B1413" s="7"/>
+    </row>
+    <row r="1414" ht="15.75" customHeight="1">
+      <c r="A1414" s="3"/>
+      <c r="B1414" s="7"/>
+    </row>
+    <row r="1415" ht="15.75" customHeight="1">
+      <c r="A1415" s="3"/>
+      <c r="B1415" s="7"/>
+    </row>
+    <row r="1416" ht="15.75" customHeight="1">
+      <c r="A1416" s="3"/>
+      <c r="B1416" s="7"/>
+    </row>
+    <row r="1417" ht="15.75" customHeight="1">
+      <c r="A1417" s="3"/>
+      <c r="B1417" s="7"/>
+    </row>
+    <row r="1418" ht="15.75" customHeight="1">
+      <c r="A1418" s="3"/>
+      <c r="B1418" s="7"/>
+    </row>
+    <row r="1419" ht="15.75" customHeight="1">
+      <c r="A1419" s="3"/>
+      <c r="B1419" s="7"/>
+    </row>
+    <row r="1420" ht="15.75" customHeight="1">
+      <c r="A1420" s="3"/>
+      <c r="B1420" s="7"/>
+    </row>
+    <row r="1421" ht="15.75" customHeight="1">
+      <c r="A1421" s="3"/>
+      <c r="B1421" s="7"/>
+    </row>
+    <row r="1422" ht="15.75" customHeight="1">
+      <c r="A1422" s="3"/>
+      <c r="B1422" s="7"/>
+    </row>
+    <row r="1423" ht="15.75" customHeight="1">
+      <c r="A1423" s="3"/>
+      <c r="B1423" s="7"/>
+    </row>
+    <row r="1424" ht="15.75" customHeight="1">
+      <c r="A1424" s="3"/>
+      <c r="B1424" s="7"/>
+    </row>
+    <row r="1425" ht="15.75" customHeight="1">
+      <c r="A1425" s="3"/>
+      <c r="B1425" s="7"/>
+    </row>
+    <row r="1426" ht="15.75" customHeight="1">
+      <c r="A1426" s="3"/>
+      <c r="B1426" s="7"/>
+    </row>
+    <row r="1427" ht="15.75" customHeight="1">
+      <c r="A1427" s="3"/>
+      <c r="B1427" s="7"/>
+    </row>
+    <row r="1428" ht="15.75" customHeight="1">
+      <c r="A1428" s="3"/>
+      <c r="B1428" s="7"/>
+    </row>
+    <row r="1429" ht="15.75" customHeight="1">
+      <c r="A1429" s="3"/>
+      <c r="B1429" s="7"/>
+    </row>
+    <row r="1430" ht="15.75" customHeight="1">
+      <c r="A1430" s="3"/>
+      <c r="B1430" s="7"/>
+    </row>
+    <row r="1431" ht="15.75" customHeight="1">
+      <c r="A1431" s="3"/>
+      <c r="B1431" s="7"/>
+    </row>
+    <row r="1432" ht="15.75" customHeight="1">
+      <c r="A1432" s="3"/>
+      <c r="B1432" s="7"/>
+    </row>
+    <row r="1433" ht="15.75" customHeight="1">
+      <c r="A1433" s="3"/>
+      <c r="B1433" s="7"/>
+    </row>
+    <row r="1434" ht="15.75" customHeight="1">
+      <c r="A1434" s="3"/>
+      <c r="B1434" s="7"/>
+    </row>
+    <row r="1435" ht="15.75" customHeight="1">
+      <c r="A1435" s="3"/>
+      <c r="B1435" s="7"/>
+    </row>
+    <row r="1436" ht="15.75" customHeight="1">
+      <c r="A1436" s="3"/>
+      <c r="B1436" s="7"/>
+    </row>
+    <row r="1437" ht="15.75" customHeight="1">
+      <c r="A1437" s="3"/>
+      <c r="B1437" s="7"/>
+    </row>
+    <row r="1438" ht="15.75" customHeight="1">
+      <c r="A1438" s="3"/>
+      <c r="B1438" s="7"/>
+    </row>
+    <row r="1439" ht="15.75" customHeight="1">
+      <c r="A1439" s="3"/>
+      <c r="B1439" s="7"/>
+    </row>
+    <row r="1440" ht="15.75" customHeight="1">
+      <c r="A1440" s="3"/>
+      <c r="B1440" s="7"/>
+    </row>
+    <row r="1441" ht="15.75" customHeight="1">
+      <c r="A1441" s="3"/>
+      <c r="B1441" s="7"/>
+    </row>
+    <row r="1442" ht="15.75" customHeight="1">
+      <c r="A1442" s="3"/>
+      <c r="B1442" s="7"/>
+    </row>
+    <row r="1443" ht="15.75" customHeight="1">
+      <c r="A1443" s="3"/>
+      <c r="B1443" s="7"/>
+    </row>
+    <row r="1444" ht="15.75" customHeight="1">
+      <c r="A1444" s="3"/>
+      <c r="B1444" s="7"/>
+    </row>
+    <row r="1445" ht="15.75" customHeight="1">
+      <c r="A1445" s="3"/>
+      <c r="B1445" s="7"/>
+    </row>
+    <row r="1446" ht="15.75" customHeight="1">
+      <c r="A1446" s="3"/>
+      <c r="B1446" s="7"/>
+    </row>
+    <row r="1447" ht="15.75" customHeight="1">
+      <c r="A1447" s="3"/>
+      <c r="B1447" s="7"/>
+    </row>
+    <row r="1448" ht="15.75" customHeight="1">
+      <c r="A1448" s="3"/>
+      <c r="B1448" s="7"/>
+    </row>
+    <row r="1449" ht="15.75" customHeight="1">
+      <c r="A1449" s="3"/>
+      <c r="B1449" s="7"/>
+    </row>
+    <row r="1450" ht="15.75" customHeight="1">
+      <c r="A1450" s="3"/>
+      <c r="B1450" s="7"/>
+    </row>
+    <row r="1451" ht="15.75" customHeight="1">
+      <c r="A1451" s="3"/>
+      <c r="B1451" s="7"/>
+    </row>
+    <row r="1452" ht="15.75" customHeight="1">
+      <c r="A1452" s="3"/>
+      <c r="B1452" s="7"/>
+    </row>
+    <row r="1453" ht="15.75" customHeight="1">
+      <c r="A1453" s="3"/>
+      <c r="B1453" s="7"/>
+    </row>
+    <row r="1454" ht="15.75" customHeight="1">
+      <c r="A1454" s="3"/>
+      <c r="B1454" s="7"/>
+    </row>
+    <row r="1455" ht="15.75" customHeight="1">
+      <c r="A1455" s="3"/>
+      <c r="B1455" s="7"/>
+    </row>
+    <row r="1456" ht="15.75" customHeight="1">
+      <c r="A1456" s="3"/>
+      <c r="B1456" s="7"/>
+    </row>
+    <row r="1457" ht="15.75" customHeight="1">
+      <c r="A1457" s="3"/>
+      <c r="B1457" s="7"/>
+    </row>
+    <row r="1458" ht="15.75" customHeight="1">
+      <c r="A1458" s="3"/>
+      <c r="B1458" s="7"/>
+    </row>
+    <row r="1459" ht="15.75" customHeight="1">
+      <c r="A1459" s="3"/>
+      <c r="B1459" s="7"/>
+    </row>
+    <row r="1460" ht="15.75" customHeight="1">
+      <c r="A1460" s="3"/>
+      <c r="B1460" s="7"/>
+    </row>
+    <row r="1461" ht="15.75" customHeight="1">
+      <c r="A1461" s="3"/>
+      <c r="B1461" s="7"/>
+    </row>
+    <row r="1462" ht="15.75" customHeight="1">
+      <c r="A1462" s="3"/>
+      <c r="B1462" s="7"/>
+    </row>
+    <row r="1463" ht="15.75" customHeight="1">
+      <c r="A1463" s="3"/>
+      <c r="B1463" s="7"/>
+    </row>
+    <row r="1464" ht="15.75" customHeight="1">
+      <c r="A1464" s="3"/>
+      <c r="B1464" s="7"/>
+    </row>
+    <row r="1465" ht="15.75" customHeight="1">
+      <c r="A1465" s="3"/>
+      <c r="B1465" s="7"/>
+    </row>
+    <row r="1466" ht="15.75" customHeight="1">
+      <c r="A1466" s="3"/>
+      <c r="B1466" s="7"/>
+    </row>
+    <row r="1467" ht="15.75" customHeight="1">
+      <c r="A1467" s="3"/>
+      <c r="B1467" s="7"/>
+    </row>
+    <row r="1468" ht="15.75" customHeight="1">
+      <c r="A1468" s="3"/>
+      <c r="B1468" s="7"/>
+    </row>
+    <row r="1469" ht="15.75" customHeight="1">
+      <c r="A1469" s="3"/>
+      <c r="B1469" s="7"/>
+    </row>
+    <row r="1470" ht="15.75" customHeight="1">
+      <c r="A1470" s="3"/>
+      <c r="B1470" s="7"/>
+    </row>
+    <row r="1471" ht="15.75" customHeight="1">
+      <c r="A1471" s="3"/>
+      <c r="B1471" s="7"/>
+    </row>
+    <row r="1472" ht="15.75" customHeight="1">
+      <c r="A1472" s="3"/>
+      <c r="B1472" s="7"/>
+    </row>
+    <row r="1473" ht="15.75" customHeight="1">
+      <c r="A1473" s="3"/>
+      <c r="B1473" s="7"/>
+    </row>
+    <row r="1474" ht="15.75" customHeight="1">
+      <c r="A1474" s="3"/>
+      <c r="B1474" s="7"/>
+    </row>
+    <row r="1475" ht="15.75" customHeight="1">
+      <c r="A1475" s="3"/>
+      <c r="B1475" s="7"/>
+    </row>
+    <row r="1476" ht="15.75" customHeight="1">
+      <c r="A1476" s="3"/>
+      <c r="B1476" s="7"/>
+    </row>
+    <row r="1477" ht="15.75" customHeight="1">
+      <c r="A1477" s="3"/>
+      <c r="B1477" s="7"/>
+    </row>
+    <row r="1478" ht="15.75" customHeight="1">
+      <c r="A1478" s="3"/>
+      <c r="B1478" s="7"/>
+    </row>
+    <row r="1479" ht="15.75" customHeight="1">
+      <c r="A1479" s="3"/>
+      <c r="B1479" s="7"/>
+    </row>
+    <row r="1480" ht="15.75" customHeight="1">
+      <c r="A1480" s="3"/>
+      <c r="B1480" s="7"/>
+    </row>
+    <row r="1481" ht="15.75" customHeight="1">
+      <c r="A1481" s="3"/>
+      <c r="B1481" s="7"/>
+    </row>
+    <row r="1482" ht="15.75" customHeight="1">
+      <c r="A1482" s="3"/>
+      <c r="B1482" s="7"/>
+    </row>
+    <row r="1483" ht="15.75" customHeight="1">
+      <c r="A1483" s="3"/>
+      <c r="B1483" s="7"/>
+    </row>
+    <row r="1484" ht="15.75" customHeight="1">
+      <c r="A1484" s="3"/>
+      <c r="B1484" s="7"/>
+    </row>
+    <row r="1485" ht="15.75" customHeight="1">
+      <c r="A1485" s="3"/>
+      <c r="B1485" s="7"/>
+    </row>
+    <row r="1486" ht="15.75" customHeight="1">
+      <c r="A1486" s="3"/>
+      <c r="B1486" s="7"/>
+    </row>
+    <row r="1487" ht="15.75" customHeight="1">
+      <c r="A1487" s="3"/>
+      <c r="B1487" s="7"/>
+    </row>
+    <row r="1488" ht="15.75" customHeight="1">
+      <c r="A1488" s="3"/>
+      <c r="B1488" s="7"/>
+    </row>
+    <row r="1489" ht="15.75" customHeight="1">
+      <c r="A1489" s="3"/>
+      <c r="B1489" s="7"/>
+    </row>
+    <row r="1490" ht="15.75" customHeight="1">
+      <c r="A1490" s="3"/>
+      <c r="B1490" s="7"/>
+    </row>
+    <row r="1491" ht="15.75" customHeight="1">
+      <c r="A1491" s="3"/>
+      <c r="B1491" s="7"/>
+    </row>
+    <row r="1492" ht="15.75" customHeight="1">
+      <c r="A1492" s="3"/>
+      <c r="B1492" s="7"/>
+    </row>
+    <row r="1493" ht="15.75" customHeight="1">
+      <c r="A1493" s="3"/>
+      <c r="B1493" s="7"/>
+    </row>
+    <row r="1494" ht="15.75" customHeight="1">
+      <c r="A1494" s="3"/>
+      <c r="B1494" s="7"/>
+    </row>
+    <row r="1495" ht="15.75" customHeight="1">
+      <c r="A1495" s="3"/>
+      <c r="B1495" s="7"/>
+    </row>
+    <row r="1496" ht="15.75" customHeight="1">
+      <c r="A1496" s="3"/>
+      <c r="B1496" s="7"/>
+    </row>
+    <row r="1497" ht="15.75" customHeight="1">
+      <c r="A1497" s="3"/>
+      <c r="B1497" s="7"/>
+    </row>
+    <row r="1498" ht="15.75" customHeight="1">
+      <c r="A1498" s="3"/>
+      <c r="B1498" s="7"/>
+    </row>
+    <row r="1499" ht="15.75" customHeight="1">
+      <c r="A1499" s="3"/>
+      <c r="B1499" s="7"/>
+    </row>
+    <row r="1500" ht="15.75" customHeight="1">
+      <c r="A1500" s="3"/>
+      <c r="B1500" s="7"/>
+    </row>
+    <row r="1501" ht="15.75" customHeight="1">
+      <c r="A1501" s="3"/>
+      <c r="B1501" s="7"/>
+    </row>
+    <row r="1502" ht="15.75" customHeight="1">
+      <c r="A1502" s="3"/>
+      <c r="B1502" s="7"/>
+    </row>
+    <row r="1503" ht="15.75" customHeight="1">
+      <c r="A1503" s="3"/>
+      <c r="B1503" s="7"/>
+    </row>
+    <row r="1504" ht="15.75" customHeight="1">
+      <c r="A1504" s="3"/>
+      <c r="B1504" s="7"/>
+    </row>
+    <row r="1505" ht="15.75" customHeight="1">
+      <c r="A1505" s="3"/>
+      <c r="B1505" s="7"/>
+    </row>
+    <row r="1506" ht="15.75" customHeight="1">
+      <c r="A1506" s="3"/>
+      <c r="B1506" s="7"/>
+    </row>
+    <row r="1507" ht="15.75" customHeight="1">
+      <c r="A1507" s="3"/>
+      <c r="B1507" s="7"/>
+    </row>
+    <row r="1508" ht="15.75" customHeight="1">
+      <c r="A1508" s="3"/>
+      <c r="B1508" s="7"/>
+    </row>
+    <row r="1509" ht="15.75" customHeight="1">
+      <c r="A1509" s="3"/>
+      <c r="B1509" s="7"/>
+    </row>
+    <row r="1510" ht="15.75" customHeight="1">
+      <c r="A1510" s="3"/>
+      <c r="B1510" s="7"/>
+    </row>
+    <row r="1511" ht="15.75" customHeight="1">
+      <c r="A1511" s="3"/>
+      <c r="B1511" s="7"/>
+    </row>
+    <row r="1512" ht="15.75" customHeight="1">
+      <c r="A1512" s="3"/>
+      <c r="B1512" s="7"/>
+    </row>
+    <row r="1513" ht="15.75" customHeight="1">
+      <c r="A1513" s="3"/>
+      <c r="B1513" s="7"/>
+    </row>
+    <row r="1514" ht="15.75" customHeight="1">
+      <c r="A1514" s="3"/>
+      <c r="B1514" s="7"/>
+    </row>
+    <row r="1515" ht="15.75" customHeight="1">
+      <c r="A1515" s="3"/>
+      <c r="B1515" s="7"/>
+    </row>
+    <row r="1516" ht="15.75" customHeight="1">
+      <c r="A1516" s="3"/>
+      <c r="B1516" s="7"/>
+    </row>
+    <row r="1517" ht="15.75" customHeight="1">
+      <c r="A1517" s="3"/>
+      <c r="B1517" s="7"/>
+    </row>
+    <row r="1518" ht="15.75" customHeight="1">
+      <c r="A1518" s="3"/>
+      <c r="B1518" s="7"/>
+    </row>
+    <row r="1519" ht="15.75" customHeight="1">
+      <c r="A1519" s="3"/>
+      <c r="B1519" s="7"/>
+    </row>
+    <row r="1520" ht="15.75" customHeight="1">
+      <c r="A1520" s="3"/>
+      <c r="B1520" s="7"/>
+    </row>
+    <row r="1521" ht="15.75" customHeight="1">
+      <c r="A1521" s="3"/>
+      <c r="B1521" s="7"/>
+    </row>
+    <row r="1522" ht="15.75" customHeight="1">
+      <c r="A1522" s="3"/>
+      <c r="B1522" s="7"/>
+    </row>
+    <row r="1523" ht="15.75" customHeight="1">
+      <c r="A1523" s="3"/>
+      <c r="B1523" s="7"/>
+    </row>
+    <row r="1524" ht="15.75" customHeight="1">
+      <c r="A1524" s="3"/>
+      <c r="B1524" s="7"/>
+    </row>
+    <row r="1525" ht="15.75" customHeight="1">
+      <c r="A1525" s="3"/>
+      <c r="B1525" s="7"/>
+    </row>
+    <row r="1526" ht="15.75" customHeight="1">
+      <c r="A1526" s="3"/>
+      <c r="B1526" s="7"/>
+    </row>
+    <row r="1527" ht="15.75" customHeight="1">
+      <c r="A1527" s="3"/>
+      <c r="B1527" s="7"/>
+    </row>
+    <row r="1528" ht="15.75" customHeight="1">
+      <c r="A1528" s="3"/>
+      <c r="B1528" s="7"/>
+    </row>
+    <row r="1529" ht="15.75" customHeight="1">
+      <c r="A1529" s="3"/>
+      <c r="B1529" s="7"/>
+    </row>
+    <row r="1530" ht="15.75" customHeight="1">
+      <c r="A1530" s="3"/>
+      <c r="B1530" s="7"/>
+    </row>
+    <row r="1531" ht="15.75" customHeight="1">
+      <c r="A1531" s="3"/>
+      <c r="B1531" s="7"/>
+    </row>
+    <row r="1532" ht="15.75" customHeight="1">
+      <c r="A1532" s="3"/>
+      <c r="B1532" s="7"/>
+    </row>
+    <row r="1533" ht="15.75" customHeight="1">
+      <c r="A1533" s="3"/>
+      <c r="B1533" s="7"/>
+    </row>
+    <row r="1534" ht="15.75" customHeight="1">
+      <c r="A1534" s="3"/>
+      <c r="B1534" s="7"/>
+    </row>
+    <row r="1535" ht="15.75" customHeight="1">
+      <c r="A1535" s="3"/>
+      <c r="B1535" s="7"/>
+    </row>
+    <row r="1536" ht="15.75" customHeight="1">
+      <c r="A1536" s="3"/>
+      <c r="B1536" s="7"/>
+    </row>
+    <row r="1537" ht="15.75" customHeight="1">
+      <c r="A1537" s="3"/>
+      <c r="B1537" s="7"/>
+    </row>
+    <row r="1538" ht="15.75" customHeight="1">
+      <c r="A1538" s="3"/>
+      <c r="B1538" s="7"/>
+    </row>
+    <row r="1539" ht="15.75" customHeight="1">
+      <c r="A1539" s="3"/>
+      <c r="B1539" s="7"/>
+    </row>
+    <row r="1540" ht="15.75" customHeight="1">
+      <c r="A1540" s="3"/>
+      <c r="B1540" s="7"/>
+    </row>
+    <row r="1541" ht="15.75" customHeight="1">
+      <c r="A1541" s="3"/>
+      <c r="B1541" s="7"/>
+    </row>
+    <row r="1542" ht="15.75" customHeight="1">
+      <c r="A1542" s="3"/>
+      <c r="B1542" s="7"/>
+    </row>
+    <row r="1543" ht="15.75" customHeight="1">
+      <c r="A1543" s="3"/>
+      <c r="B1543" s="7"/>
+    </row>
+    <row r="1544" ht="15.75" customHeight="1">
+      <c r="A1544" s="3"/>
+      <c r="B1544" s="7"/>
+    </row>
+    <row r="1545" ht="15.75" customHeight="1">
+      <c r="A1545" s="3"/>
+      <c r="B1545" s="7"/>
+    </row>
+    <row r="1546" ht="15.75" customHeight="1">
+      <c r="A1546" s="3"/>
+      <c r="B1546" s="7"/>
+    </row>
+    <row r="1547" ht="15.75" customHeight="1">
+      <c r="A1547" s="3"/>
+      <c r="B1547" s="7"/>
+    </row>
+    <row r="1548" ht="15.75" customHeight="1">
+      <c r="A1548" s="3"/>
+      <c r="B1548" s="7"/>
+    </row>
+    <row r="1549" ht="15.75" customHeight="1">
+      <c r="A1549" s="3"/>
+      <c r="B1549" s="7"/>
+    </row>
+    <row r="1550" ht="15.75" customHeight="1">
+      <c r="A1550" s="3"/>
+      <c r="B1550" s="7"/>
+    </row>
+    <row r="1551" ht="15.75" customHeight="1">
+      <c r="A1551" s="3"/>
+      <c r="B1551" s="7"/>
+    </row>
+    <row r="1552" ht="15.75" customHeight="1">
+      <c r="A1552" s="3"/>
+      <c r="B1552" s="7"/>
+    </row>
+    <row r="1553" ht="15.75" customHeight="1">
+      <c r="A1553" s="3"/>
+      <c r="B1553" s="7"/>
+    </row>
+    <row r="1554" ht="15.75" customHeight="1">
+      <c r="A1554" s="3"/>
+      <c r="B1554" s="7"/>
+    </row>
+    <row r="1555" ht="15.75" customHeight="1">
+      <c r="A1555" s="3"/>
+      <c r="B1555" s="7"/>
+    </row>
+    <row r="1556" ht="15.75" customHeight="1">
+      <c r="A1556" s="3"/>
+      <c r="B1556" s="7"/>
+    </row>
+    <row r="1557" ht="15.75" customHeight="1">
+      <c r="A1557" s="3"/>
+      <c r="B1557" s="7"/>
+    </row>
+    <row r="1558" ht="15.75" customHeight="1">
+      <c r="A1558" s="3"/>
+      <c r="B1558" s="7"/>
+    </row>
+    <row r="1559" ht="15.75" customHeight="1">
+      <c r="A1559" s="3"/>
+      <c r="B1559" s="7"/>
+    </row>
+    <row r="1560" ht="15.75" customHeight="1">
+      <c r="A1560" s="3"/>
+      <c r="B1560" s="7"/>
+    </row>
+    <row r="1561" ht="15.75" customHeight="1">
+      <c r="A1561" s="3"/>
+      <c r="B1561" s="7"/>
+    </row>
+    <row r="1562" ht="15.75" customHeight="1">
+      <c r="A1562" s="3"/>
+      <c r="B1562" s="7"/>
+    </row>
+    <row r="1563" ht="15.75" customHeight="1">
+      <c r="A1563" s="3"/>
+      <c r="B1563" s="7"/>
+    </row>
+    <row r="1564" ht="15.75" customHeight="1">
+      <c r="A1564" s="3"/>
+      <c r="B1564" s="7"/>
+    </row>
+    <row r="1565" ht="15.75" customHeight="1">
+      <c r="A1565" s="3"/>
+      <c r="B1565" s="7"/>
+    </row>
+    <row r="1566" ht="15.75" customHeight="1">
+      <c r="A1566" s="3"/>
+      <c r="B1566" s="7"/>
+    </row>
+    <row r="1567" ht="15.75" customHeight="1">
+      <c r="A1567" s="3"/>
+      <c r="B1567" s="7"/>
+    </row>
+    <row r="1568" ht="15.75" customHeight="1">
+      <c r="A1568" s="3"/>
+      <c r="B1568" s="7"/>
+    </row>
+    <row r="1569" ht="15.75" customHeight="1">
+      <c r="A1569" s="3"/>
+      <c r="B1569" s="7"/>
+    </row>
+    <row r="1570" ht="15.75" customHeight="1">
+      <c r="A1570" s="3"/>
+      <c r="B1570" s="7"/>
+    </row>
+    <row r="1571" ht="15.75" customHeight="1">
+      <c r="A1571" s="3"/>
+      <c r="B1571" s="7"/>
+    </row>
+    <row r="1572" ht="15.75" customHeight="1">
+      <c r="A1572" s="3"/>
+      <c r="B1572" s="7"/>
+    </row>
+    <row r="1573" ht="15.75" customHeight="1">
+      <c r="A1573" s="3"/>
+      <c r="B1573" s="7"/>
+    </row>
+    <row r="1574" ht="15.75" customHeight="1">
+      <c r="A1574" s="3"/>
+      <c r="B1574" s="7"/>
+    </row>
+    <row r="1575" ht="15.75" customHeight="1">
+      <c r="A1575" s="3"/>
+      <c r="B1575" s="7"/>
+    </row>
+    <row r="1576" ht="15.75" customHeight="1">
+      <c r="A1576" s="3"/>
+      <c r="B1576" s="7"/>
+    </row>
+    <row r="1577" ht="15.75" customHeight="1">
+      <c r="A1577" s="3"/>
+      <c r="B1577" s="7"/>
+    </row>
+    <row r="1578" ht="15.75" customHeight="1">
+      <c r="A1578" s="3"/>
+      <c r="B1578" s="7"/>
+    </row>
+    <row r="1579" ht="15.75" customHeight="1">
+      <c r="A1579" s="3"/>
+      <c r="B1579" s="7"/>
+    </row>
+    <row r="1580" ht="15.75" customHeight="1">
+      <c r="A1580" s="3"/>
+      <c r="B1580" s="7"/>
+    </row>
+    <row r="1581" ht="15.75" customHeight="1">
+      <c r="A1581" s="3"/>
+      <c r="B1581" s="7"/>
+    </row>
+    <row r="1582" ht="15.75" customHeight="1">
+      <c r="A1582" s="3"/>
+      <c r="B1582" s="7"/>
+    </row>
+    <row r="1583" ht="15.75" customHeight="1">
+      <c r="A1583" s="3"/>
+      <c r="B1583" s="7"/>
+    </row>
+    <row r="1584" ht="15.75" customHeight="1">
+      <c r="A1584" s="3"/>
+      <c r="B1584" s="7"/>
+    </row>
+    <row r="1585" ht="15.75" customHeight="1">
+      <c r="A1585" s="3"/>
+      <c r="B1585" s="7"/>
+    </row>
+    <row r="1586" ht="15.75" customHeight="1">
+      <c r="A1586" s="3"/>
+      <c r="B1586" s="7"/>
+    </row>
+    <row r="1587" ht="15.75" customHeight="1">
+      <c r="A1587" s="3"/>
+      <c r="B1587" s="7"/>
+    </row>
+    <row r="1588" ht="15.75" customHeight="1">
+      <c r="A1588" s="3"/>
+      <c r="B1588" s="7"/>
+    </row>
+    <row r="1589" ht="15.75" customHeight="1">
+      <c r="A1589" s="3"/>
+      <c r="B1589" s="7"/>
+    </row>
+    <row r="1590" ht="15.75" customHeight="1">
+      <c r="A1590" s="3"/>
+      <c r="B1590" s="7"/>
+    </row>
+    <row r="1591" ht="15.75" customHeight="1">
+      <c r="A1591" s="3"/>
+      <c r="B1591" s="7"/>
+    </row>
+    <row r="1592" ht="15.75" customHeight="1">
+      <c r="A1592" s="3"/>
+      <c r="B1592" s="7"/>
+    </row>
+    <row r="1593" ht="15.75" customHeight="1">
+      <c r="A1593" s="3"/>
+      <c r="B1593" s="7"/>
+    </row>
+    <row r="1594" ht="15.75" customHeight="1">
+      <c r="A1594" s="3"/>
+      <c r="B1594" s="7"/>
+    </row>
+    <row r="1595" ht="15.75" customHeight="1">
+      <c r="A1595" s="3"/>
+      <c r="B1595" s="7"/>
+    </row>
+    <row r="1596" ht="15.75" customHeight="1">
+      <c r="A1596" s="3"/>
+      <c r="B1596" s="7"/>
+    </row>
+    <row r="1597" ht="15.75" customHeight="1">
+      <c r="A1597" s="3"/>
+      <c r="B1597" s="7"/>
+    </row>
+    <row r="1598" ht="15.75" customHeight="1">
+      <c r="A1598" s="3"/>
+      <c r="B1598" s="7"/>
+    </row>
+    <row r="1599" ht="15.75" customHeight="1">
+      <c r="A1599" s="3"/>
+      <c r="B1599" s="7"/>
+    </row>
+    <row r="1600" ht="15.75" customHeight="1">
+      <c r="A1600" s="3"/>
+      <c r="B1600" s="7"/>
+    </row>
+    <row r="1601" ht="15.75" customHeight="1">
+      <c r="A1601" s="3"/>
+      <c r="B1601" s="7"/>
+    </row>
+    <row r="1602" ht="15.75" customHeight="1">
+      <c r="A1602" s="3"/>
+      <c r="B1602" s="7"/>
+    </row>
+    <row r="1603" ht="15.75" customHeight="1">
+      <c r="A1603" s="3"/>
+      <c r="B1603" s="7"/>
+    </row>
+    <row r="1604" ht="15.75" customHeight="1">
+      <c r="A1604" s="3"/>
+      <c r="B1604" s="7"/>
+    </row>
+    <row r="1605" ht="15.75" customHeight="1">
+      <c r="A1605" s="3"/>
+      <c r="B1605" s="7"/>
+    </row>
+    <row r="1606" ht="15.75" customHeight="1">
+      <c r="A1606" s="3"/>
+      <c r="B1606" s="7"/>
+    </row>
+    <row r="1607" ht="15.75" customHeight="1">
+      <c r="A1607" s="3"/>
+      <c r="B1607" s="7"/>
+    </row>
+    <row r="1608" ht="15.75" customHeight="1">
+      <c r="A1608" s="3"/>
+      <c r="B1608" s="7"/>
+    </row>
+    <row r="1609" ht="15.75" customHeight="1">
+      <c r="A1609" s="3"/>
+      <c r="B1609" s="7"/>
+    </row>
+    <row r="1610" ht="15.75" customHeight="1">
+      <c r="A1610" s="3"/>
+      <c r="B1610" s="7"/>
+    </row>
+    <row r="1611" ht="15.75" customHeight="1">
+      <c r="A1611" s="3"/>
+      <c r="B1611" s="7"/>
+    </row>
+    <row r="1612" ht="15.75" customHeight="1">
+      <c r="A1612" s="3"/>
+      <c r="B1612" s="7"/>
+    </row>
+    <row r="1613" ht="15.75" customHeight="1">
+      <c r="A1613" s="3"/>
+      <c r="B1613" s="7"/>
+    </row>
+    <row r="1614" ht="15.75" customHeight="1">
+      <c r="A1614" s="3"/>
+      <c r="B1614" s="7"/>
+    </row>
+    <row r="1615" ht="15.75" customHeight="1">
+      <c r="A1615" s="3"/>
+      <c r="B1615" s="7"/>
+    </row>
+    <row r="1616" ht="15.75" customHeight="1">
+      <c r="A1616" s="3"/>
+      <c r="B1616" s="7"/>
+    </row>
+    <row r="1617" ht="15.75" customHeight="1">
+      <c r="A1617" s="3"/>
+      <c r="B1617" s="7"/>
+    </row>
+    <row r="1618" ht="15.75" customHeight="1">
+      <c r="A1618" s="3"/>
+      <c r="B1618" s="7"/>
+    </row>
+    <row r="1619" ht="15.75" customHeight="1">
+      <c r="A1619" s="3"/>
+      <c r="B1619" s="7"/>
+    </row>
+    <row r="1620" ht="15.75" customHeight="1">
+      <c r="A1620" s="3"/>
+      <c r="B1620" s="7"/>
+    </row>
+    <row r="1621" ht="15.75" customHeight="1">
+      <c r="A1621" s="3"/>
+      <c r="B1621" s="7"/>
+    </row>
+    <row r="1622" ht="15.75" customHeight="1">
+      <c r="A1622" s="3"/>
+      <c r="B1622" s="7"/>
+    </row>
+    <row r="1623" ht="15.75" customHeight="1">
+      <c r="A1623" s="3"/>
+      <c r="B1623" s="7"/>
+    </row>
+    <row r="1624" ht="15.75" customHeight="1">
+      <c r="A1624" s="3"/>
+      <c r="B1624" s="7"/>
+    </row>
+    <row r="1625" ht="15.75" customHeight="1">
+      <c r="A1625" s="3"/>
+      <c r="B1625" s="7"/>
+    </row>
+    <row r="1626" ht="15.75" customHeight="1">
+      <c r="A1626" s="3"/>
+      <c r="B1626" s="7"/>
+    </row>
+    <row r="1627" ht="15.75" customHeight="1">
+      <c r="A1627" s="3"/>
+      <c r="B1627" s="7"/>
+    </row>
+    <row r="1628" ht="15.75" customHeight="1">
+      <c r="A1628" s="3"/>
+      <c r="B1628" s="7"/>
+    </row>
+    <row r="1629" ht="15.75" customHeight="1">
+      <c r="A1629" s="3"/>
+      <c r="B1629" s="7"/>
+    </row>
+    <row r="1630" ht="15.75" customHeight="1">
+      <c r="A1630" s="3"/>
+      <c r="B1630" s="7"/>
+    </row>
+    <row r="1631" ht="15.75" customHeight="1">
+      <c r="A1631" s="3"/>
+      <c r="B1631" s="7"/>
+    </row>
+    <row r="1632" ht="15.75" customHeight="1">
+      <c r="A1632" s="3"/>
+      <c r="B1632" s="7"/>
+    </row>
+    <row r="1633" ht="15.75" customHeight="1">
+      <c r="A1633" s="3"/>
+      <c r="B1633" s="7"/>
+    </row>
+    <row r="1634" ht="15.75" customHeight="1">
+      <c r="A1634" s="3"/>
+      <c r="B1634" s="7"/>
+    </row>
+    <row r="1635" ht="15.75" customHeight="1">
+      <c r="A1635" s="3"/>
+      <c r="B1635" s="7"/>
+    </row>
+    <row r="1636" ht="15.75" customHeight="1">
+      <c r="A1636" s="3"/>
+      <c r="B1636" s="7"/>
+    </row>
+    <row r="1637" ht="15.75" customHeight="1">
+      <c r="A1637" s="3"/>
+      <c r="B1637" s="7"/>
+    </row>
+    <row r="1638" ht="15.75" customHeight="1">
+      <c r="A1638" s="3"/>
+      <c r="B1638" s="7"/>
+    </row>
+    <row r="1639" ht="15.75" customHeight="1">
+      <c r="A1639" s="3"/>
+      <c r="B1639" s="7"/>
+    </row>
+    <row r="1640" ht="15.75" customHeight="1">
+      <c r="A1640" s="3"/>
+      <c r="B1640" s="7"/>
+    </row>
+    <row r="1641" ht="15.75" customHeight="1">
+      <c r="A1641" s="3"/>
+      <c r="B1641" s="7"/>
+    </row>
+    <row r="1642" ht="15.75" customHeight="1">
+      <c r="A1642" s="3"/>
+      <c r="B1642" s="7"/>
+    </row>
+    <row r="1643" ht="15.75" customHeight="1">
+      <c r="A1643" s="3"/>
+      <c r="B1643" s="7"/>
+    </row>
+    <row r="1644" ht="15.75" customHeight="1">
+      <c r="A1644" s="3"/>
+      <c r="B1644" s="7"/>
+    </row>
+    <row r="1645" ht="15.75" customHeight="1">
+      <c r="A1645" s="3"/>
+      <c r="B1645" s="7"/>
+    </row>
+    <row r="1646" ht="15.75" customHeight="1">
+      <c r="A1646" s="3"/>
+      <c r="B1646" s="7"/>
+    </row>
+    <row r="1647" ht="15.75" customHeight="1">
+      <c r="A1647" s="3"/>
+      <c r="B1647" s="7"/>
+    </row>
+    <row r="1648" ht="15.75" customHeight="1">
+      <c r="A1648" s="3"/>
+      <c r="B1648" s="7"/>
+    </row>
+    <row r="1649" ht="15.75" customHeight="1">
+      <c r="A1649" s="3"/>
+      <c r="B1649" s="7"/>
+    </row>
+    <row r="1650" ht="15.75" customHeight="1">
+      <c r="A1650" s="3"/>
+      <c r="B1650" s="7"/>
+    </row>
+    <row r="1651" ht="15.75" customHeight="1">
+      <c r="A1651" s="3"/>
+      <c r="B1651" s="7"/>
+    </row>
+    <row r="1652" ht="15.75" customHeight="1">
+      <c r="A1652" s="3"/>
+      <c r="B1652" s="7"/>
+    </row>
+    <row r="1653" ht="15.75" customHeight="1">
+      <c r="A1653" s="3"/>
+      <c r="B1653" s="7"/>
+    </row>
+    <row r="1654" ht="15.75" customHeight="1">
+      <c r="A1654" s="3"/>
+      <c r="B1654" s="7"/>
+    </row>
+    <row r="1655" ht="15.75" customHeight="1">
+      <c r="A1655" s="3"/>
+      <c r="B1655" s="7"/>
+    </row>
+    <row r="1656" ht="15.75" customHeight="1">
+      <c r="A1656" s="3"/>
+      <c r="B1656" s="7"/>
+    </row>
+    <row r="1657" ht="15.75" customHeight="1">
+      <c r="A1657" s="3"/>
+      <c r="B1657" s="7"/>
+    </row>
+    <row r="1658" ht="15.75" customHeight="1">
+      <c r="A1658" s="3"/>
+      <c r="B1658" s="7"/>
+    </row>
+    <row r="1659" ht="15.75" customHeight="1">
+      <c r="A1659" s="3"/>
+      <c r="B1659" s="7"/>
+    </row>
+    <row r="1660" ht="15.75" customHeight="1">
+      <c r="A1660" s="3"/>
+      <c r="B1660" s="7"/>
+    </row>
+    <row r="1661" ht="15.75" customHeight="1">
+      <c r="A1661" s="3"/>
+      <c r="B1661" s="7"/>
+    </row>
+    <row r="1662" ht="15.75" customHeight="1">
+      <c r="A1662" s="3"/>
+      <c r="B1662" s="7"/>
+    </row>
+    <row r="1663" ht="15.75" customHeight="1">
+      <c r="A1663" s="3"/>
+      <c r="B1663" s="7"/>
+    </row>
+    <row r="1664" ht="15.75" customHeight="1">
+      <c r="A1664" s="3"/>
+      <c r="B1664" s="7"/>
+    </row>
+    <row r="1665" ht="15.75" customHeight="1">
+      <c r="A1665" s="3"/>
+      <c r="B1665" s="7"/>
+    </row>
+    <row r="1666" ht="15.75" customHeight="1">
+      <c r="A1666" s="3"/>
+      <c r="B1666" s="7"/>
+    </row>
+    <row r="1667" ht="15.75" customHeight="1">
+      <c r="A1667" s="3"/>
+      <c r="B1667" s="7"/>
+    </row>
+    <row r="1668" ht="15.75" customHeight="1">
+      <c r="A1668" s="3"/>
+      <c r="B1668" s="7"/>
+    </row>
+    <row r="1669" ht="15.75" customHeight="1">
+      <c r="A1669" s="3"/>
+      <c r="B1669" s="7"/>
+    </row>
+    <row r="1670" ht="15.75" customHeight="1">
+      <c r="A1670" s="3"/>
+      <c r="B1670" s="7"/>
+    </row>
+    <row r="1671" ht="15.75" customHeight="1">
+      <c r="A1671" s="3"/>
+      <c r="B1671" s="7"/>
+    </row>
+    <row r="1672" ht="15.75" customHeight="1">
+      <c r="A1672" s="3"/>
+      <c r="B1672" s="7"/>
+    </row>
+    <row r="1673" ht="15.75" customHeight="1">
+      <c r="A1673" s="3"/>
+      <c r="B1673" s="7"/>
+    </row>
+    <row r="1674" ht="15.75" customHeight="1">
+      <c r="A1674" s="3"/>
+      <c r="B1674" s="7"/>
+    </row>
+    <row r="1675" ht="15.75" customHeight="1">
+      <c r="A1675" s="3"/>
+      <c r="B1675" s="7"/>
+    </row>
+    <row r="1676" ht="15.75" customHeight="1">
+      <c r="A1676" s="3"/>
+      <c r="B1676" s="7"/>
+    </row>
+    <row r="1677" ht="15.75" customHeight="1">
+      <c r="A1677" s="3"/>
+      <c r="B1677" s="7"/>
+    </row>
+    <row r="1678" ht="15.75" customHeight="1">
+      <c r="A1678" s="3"/>
+      <c r="B1678" s="7"/>
+    </row>
+    <row r="1679" ht="15.75" customHeight="1">
+      <c r="A1679" s="3"/>
+      <c r="B1679" s="7"/>
+    </row>
+    <row r="1680" ht="15.75" customHeight="1">
+      <c r="A1680" s="3"/>
+      <c r="B1680" s="7"/>
+    </row>
+    <row r="1681" ht="15.75" customHeight="1">
+      <c r="A1681" s="3"/>
+      <c r="B1681" s="7"/>
+    </row>
+    <row r="1682" ht="15.75" customHeight="1">
+      <c r="A1682" s="3"/>
+      <c r="B1682" s="7"/>
+    </row>
+    <row r="1683" ht="15.75" customHeight="1">
+      <c r="A1683" s="3"/>
+      <c r="B1683" s="7"/>
+    </row>
+    <row r="1684" ht="15.75" customHeight="1">
+      <c r="A1684" s="3"/>
+      <c r="B1684" s="7"/>
+    </row>
+    <row r="1685" ht="15.75" customHeight="1">
+      <c r="A1685" s="3"/>
+      <c r="B1685" s="7"/>
+    </row>
+    <row r="1686" ht="15.75" customHeight="1">
+      <c r="A1686" s="3"/>
+      <c r="B1686" s="7"/>
+    </row>
+    <row r="1687" ht="15.75" customHeight="1">
+      <c r="A1687" s="3"/>
+      <c r="B1687" s="7"/>
+    </row>
+    <row r="1688" ht="15.75" customHeight="1">
+      <c r="A1688" s="3"/>
+      <c r="B1688" s="7"/>
+    </row>
+    <row r="1689" ht="15.75" customHeight="1">
+      <c r="A1689" s="3"/>
+      <c r="B1689" s="7"/>
+    </row>
+    <row r="1690" ht="15.75" customHeight="1">
+      <c r="A1690" s="3"/>
+      <c r="B1690" s="7"/>
+    </row>
+    <row r="1691" ht="15.75" customHeight="1">
+      <c r="A1691" s="3"/>
+      <c r="B1691" s="7"/>
+    </row>
+    <row r="1692" ht="15.75" customHeight="1">
+      <c r="A1692" s="3"/>
+      <c r="B1692" s="7"/>
+    </row>
+    <row r="1693" ht="15.75" customHeight="1">
+      <c r="A1693" s="3"/>
+      <c r="B1693" s="7"/>
+    </row>
+    <row r="1694" ht="15.75" customHeight="1">
+      <c r="A1694" s="3"/>
+      <c r="B1694" s="7"/>
+    </row>
+    <row r="1695" ht="15.75" customHeight="1">
+      <c r="A1695" s="3"/>
+      <c r="B1695" s="7"/>
+    </row>
+    <row r="1696" ht="15.75" customHeight="1">
+      <c r="A1696" s="3"/>
+      <c r="B1696" s="7"/>
+    </row>
+    <row r="1697" ht="15.75" customHeight="1">
+      <c r="A1697" s="3"/>
+      <c r="B1697" s="7"/>
+    </row>
+    <row r="1698" ht="15.75" customHeight="1">
+      <c r="A1698" s="3"/>
+      <c r="B1698" s="7"/>
+    </row>
+    <row r="1699" ht="15.75" customHeight="1">
+      <c r="A1699" s="3"/>
+      <c r="B1699" s="7"/>
+    </row>
+    <row r="1700" ht="15.75" customHeight="1">
+      <c r="A1700" s="3"/>
+      <c r="B1700" s="7"/>
+    </row>
+    <row r="1701" ht="15.75" customHeight="1">
+      <c r="A1701" s="3"/>
+      <c r="B1701" s="7"/>
+    </row>
+    <row r="1702" ht="15.75" customHeight="1">
+      <c r="A1702" s="3"/>
+      <c r="B1702" s="7"/>
+    </row>
+    <row r="1703" ht="15.75" customHeight="1">
+      <c r="A1703" s="3"/>
+      <c r="B1703" s="7"/>
+    </row>
+    <row r="1704" ht="15.75" customHeight="1">
+      <c r="A1704" s="3"/>
+      <c r="B1704" s="7"/>
+    </row>
+    <row r="1705" ht="15.75" customHeight="1">
+      <c r="A1705" s="3"/>
+      <c r="B1705" s="7"/>
+    </row>
+    <row r="1706" ht="15.75" customHeight="1">
+      <c r="A1706" s="3"/>
+      <c r="B1706" s="7"/>
+    </row>
+    <row r="1707" ht="15.75" customHeight="1">
+      <c r="A1707" s="3"/>
+      <c r="B1707" s="7"/>
+    </row>
+    <row r="1708" ht="15.75" customHeight="1">
+      <c r="A1708" s="3"/>
+      <c r="B1708" s="7"/>
+    </row>
+    <row r="1709" ht="15.75" customHeight="1">
+      <c r="A1709" s="3"/>
+      <c r="B1709" s="7"/>
+    </row>
+    <row r="1710" ht="15.75" customHeight="1">
+      <c r="A1710" s="3"/>
+      <c r="B1710" s="7"/>
+    </row>
+    <row r="1711" ht="15.75" customHeight="1">
+      <c r="A1711" s="3"/>
+      <c r="B1711" s="7"/>
+    </row>
+    <row r="1712" ht="15.75" customHeight="1">
+      <c r="A1712" s="3"/>
+      <c r="B1712" s="7"/>
+    </row>
+    <row r="1713" ht="15.75" customHeight="1">
+      <c r="A1713" s="3"/>
+      <c r="B1713" s="7"/>
+    </row>
+    <row r="1714" ht="15.75" customHeight="1">
+      <c r="A1714" s="3"/>
+      <c r="B1714" s="7"/>
+    </row>
+    <row r="1715" ht="15.75" customHeight="1">
+      <c r="A1715" s="3"/>
+      <c r="B1715" s="7"/>
+    </row>
+    <row r="1716" ht="15.75" customHeight="1">
+      <c r="A1716" s="3"/>
+      <c r="B1716" s="7"/>
+    </row>
+    <row r="1717" ht="15.75" customHeight="1">
+      <c r="A1717" s="3"/>
+      <c r="B1717" s="7"/>
+    </row>
+    <row r="1718" ht="15.75" customHeight="1">
+      <c r="A1718" s="3"/>
+      <c r="B1718" s="7"/>
+    </row>
+    <row r="1719" ht="15.75" customHeight="1">
+      <c r="A1719" s="3"/>
+      <c r="B1719" s="7"/>
+    </row>
+    <row r="1720" ht="15.75" customHeight="1">
+      <c r="A1720" s="3"/>
+      <c r="B1720" s="7"/>
+    </row>
+    <row r="1721" ht="15.75" customHeight="1">
+      <c r="A1721" s="3"/>
+      <c r="B1721" s="7"/>
+    </row>
+    <row r="1722" ht="15.75" customHeight="1">
+      <c r="A1722" s="3"/>
+      <c r="B1722" s="7"/>
+    </row>
+    <row r="1723" ht="15.75" customHeight="1">
+      <c r="A1723" s="3"/>
+      <c r="B1723" s="7"/>
+    </row>
+    <row r="1724" ht="15.75" customHeight="1">
+      <c r="A1724" s="3"/>
+      <c r="B1724" s="7"/>
+    </row>
+    <row r="1725" ht="15.75" customHeight="1">
+      <c r="A1725" s="3"/>
+      <c r="B1725" s="7"/>
+    </row>
+    <row r="1726" ht="15.75" customHeight="1">
+      <c r="A1726" s="3"/>
+      <c r="B1726" s="7"/>
+    </row>
+    <row r="1727" ht="15.75" customHeight="1">
+      <c r="A1727" s="3"/>
+      <c r="B1727" s="7"/>
+    </row>
+    <row r="1728" ht="15.75" customHeight="1">
+      <c r="A1728" s="3"/>
+      <c r="B1728" s="7"/>
+    </row>
+    <row r="1729" ht="15.75" customHeight="1">
+      <c r="A1729" s="3"/>
+      <c r="B1729" s="7"/>
+    </row>
+    <row r="1730" ht="15.75" customHeight="1">
+      <c r="A1730" s="3"/>
+      <c r="B1730" s="7"/>
+    </row>
+    <row r="1731" ht="15.75" customHeight="1">
+      <c r="A1731" s="3"/>
+      <c r="B1731" s="7"/>
+    </row>
+    <row r="1732" ht="15.75" customHeight="1">
+      <c r="A1732" s="3"/>
+      <c r="B1732" s="7"/>
+    </row>
+    <row r="1733" ht="15.75" customHeight="1">
+      <c r="A1733" s="3"/>
+      <c r="B1733" s="7"/>
+    </row>
+    <row r="1734" ht="15.75" customHeight="1">
+      <c r="A1734" s="3"/>
+      <c r="B1734" s="7"/>
+    </row>
+    <row r="1735" ht="15.75" customHeight="1">
+      <c r="A1735" s="3"/>
+      <c r="B1735" s="7"/>
+    </row>
+    <row r="1736" ht="15.75" customHeight="1">
+      <c r="A1736" s="3"/>
+      <c r="B1736" s="7"/>
+    </row>
+    <row r="1737" ht="15.75" customHeight="1">
+      <c r="A1737" s="3"/>
+      <c r="B1737" s="7"/>
+    </row>
+    <row r="1738" ht="15.75" customHeight="1">
+      <c r="A1738" s="3"/>
+      <c r="B1738" s="7"/>
+    </row>
+    <row r="1739" ht="15.75" customHeight="1">
+      <c r="A1739" s="3"/>
+      <c r="B1739" s="7"/>
+    </row>
+    <row r="1740" ht="15.75" customHeight="1">
+      <c r="A1740" s="3"/>
+      <c r="B1740" s="7"/>
+    </row>
+    <row r="1741" ht="15.75" customHeight="1">
+      <c r="A1741" s="3"/>
+      <c r="B1741" s="7"/>
+    </row>
+    <row r="1742" ht="15.75" customHeight="1">
+      <c r="A1742" s="3"/>
+      <c r="B1742" s="7"/>
+    </row>
+    <row r="1743" ht="15.75" customHeight="1">
+      <c r="A1743" s="3"/>
+      <c r="B1743" s="7"/>
+    </row>
+    <row r="1744" ht="15.75" customHeight="1">
+      <c r="A1744" s="3"/>
+      <c r="B1744" s="7"/>
+    </row>
+    <row r="1745" ht="15.75" customHeight="1">
+      <c r="A1745" s="3"/>
+      <c r="B1745" s="7"/>
+    </row>
+    <row r="1746" ht="15.75" customHeight="1">
+      <c r="A1746" s="3"/>
+      <c r="B1746" s="7"/>
+    </row>
+    <row r="1747" ht="15.75" customHeight="1">
+      <c r="A1747" s="3"/>
+      <c r="B1747" s="7"/>
+    </row>
+    <row r="1748" ht="15.75" customHeight="1">
+      <c r="A1748" s="3"/>
+      <c r="B1748" s="7"/>
+    </row>
+    <row r="1749" ht="15.75" customHeight="1">
+      <c r="A1749" s="3"/>
+      <c r="B1749" s="7"/>
+    </row>
+    <row r="1750" ht="15.75" customHeight="1">
+      <c r="A1750" s="3"/>
+      <c r="B1750" s="7"/>
+    </row>
+    <row r="1751" ht="15.75" customHeight="1">
+      <c r="A1751" s="3"/>
+      <c r="B1751" s="7"/>
+    </row>
+    <row r="1752" ht="15.75" customHeight="1">
+      <c r="A1752" s="3"/>
+      <c r="B1752" s="7"/>
+    </row>
+    <row r="1753" ht="15.75" customHeight="1">
+      <c r="A1753" s="3"/>
+      <c r="B1753" s="7"/>
+    </row>
+    <row r="1754" ht="15.75" customHeight="1">
+      <c r="A1754" s="3"/>
+      <c r="B1754" s="7"/>
+    </row>
+    <row r="1755" ht="15.75" customHeight="1">
+      <c r="A1755" s="3"/>
+      <c r="B1755" s="7"/>
+    </row>
+    <row r="1756" ht="15.75" customHeight="1">
+      <c r="A1756" s="3"/>
+      <c r="B1756" s="7"/>
+    </row>
+    <row r="1757" ht="15.75" customHeight="1">
+      <c r="A1757" s="3"/>
+      <c r="B1757" s="7"/>
+    </row>
+    <row r="1758" ht="15.75" customHeight="1">
+      <c r="A1758" s="3"/>
+      <c r="B1758" s="7"/>
+    </row>
+    <row r="1759" ht="15.75" customHeight="1">
+      <c r="A1759" s="3"/>
+      <c r="B1759" s="7"/>
+    </row>
+    <row r="1760" ht="15.75" customHeight="1">
+      <c r="A1760" s="3"/>
+      <c r="B1760" s="7"/>
+    </row>
+    <row r="1761" ht="15.75" customHeight="1">
+      <c r="A1761" s="3"/>
+      <c r="B1761" s="7"/>
+    </row>
+    <row r="1762" ht="15.75" customHeight="1">
+      <c r="A1762" s="3"/>
+      <c r="B1762" s="7"/>
+    </row>
+    <row r="1763" ht="15.75" customHeight="1">
+      <c r="A1763" s="3"/>
+      <c r="B1763" s="7"/>
+    </row>
+    <row r="1764" ht="15.75" customHeight="1">
+      <c r="A1764" s="3"/>
+      <c r="B1764" s="7"/>
+    </row>
+    <row r="1765" ht="15.75" customHeight="1">
+      <c r="A1765" s="3"/>
+      <c r="B1765" s="7"/>
+    </row>
+    <row r="1766" ht="15.75" customHeight="1">
+      <c r="A1766" s="3"/>
+      <c r="B1766" s="7"/>
+    </row>
+    <row r="1767" ht="15.75" customHeight="1">
+      <c r="A1767" s="3"/>
+      <c r="B1767" s="7"/>
+    </row>
+    <row r="1768" ht="15.75" customHeight="1">
+      <c r="A1768" s="3"/>
+      <c r="B1768" s="7"/>
+    </row>
+    <row r="1769" ht="15.75" customHeight="1">
+      <c r="A1769" s="3"/>
+      <c r="B1769" s="7"/>
+    </row>
+    <row r="1770" ht="15.75" customHeight="1">
+      <c r="A1770" s="3"/>
+      <c r="B1770" s="7"/>
+    </row>
+    <row r="1771" ht="15.75" customHeight="1">
+      <c r="A1771" s="3"/>
+      <c r="B1771" s="7"/>
+    </row>
+    <row r="1772" ht="15.75" customHeight="1">
+      <c r="A1772" s="3"/>
+      <c r="B1772" s="7"/>
+    </row>
+    <row r="1773" ht="15.75" customHeight="1">
+      <c r="A1773" s="3"/>
+      <c r="B1773" s="7"/>
+    </row>
+    <row r="1774" ht="15.75" customHeight="1">
+      <c r="A1774" s="3"/>
+      <c r="B1774" s="7"/>
+    </row>
+    <row r="1775" ht="15.75" customHeight="1">
+      <c r="A1775" s="3"/>
+      <c r="B1775" s="7"/>
+    </row>
+    <row r="1776" ht="15.75" customHeight="1">
+      <c r="A1776" s="3"/>
+      <c r="B1776" s="7"/>
+    </row>
+    <row r="1777" ht="15.75" customHeight="1">
+      <c r="A1777" s="3"/>
+      <c r="B1777" s="7"/>
+    </row>
+    <row r="1778" ht="15.75" customHeight="1">
+      <c r="A1778" s="3"/>
+      <c r="B1778" s="7"/>
+    </row>
+    <row r="1779" ht="15.75" customHeight="1">
+      <c r="A1779" s="3"/>
+      <c r="B1779" s="7"/>
+    </row>
+    <row r="1780" ht="15.75" customHeight="1">
+      <c r="A1780" s="3"/>
+      <c r="B1780" s="7"/>
+    </row>
+    <row r="1781" ht="15.75" customHeight="1">
+      <c r="A1781" s="3"/>
+      <c r="B1781" s="7"/>
+    </row>
+    <row r="1782" ht="15.75" customHeight="1">
+      <c r="A1782" s="3"/>
+      <c r="B1782" s="7"/>
+    </row>
+    <row r="1783" ht="15.75" customHeight="1">
+      <c r="A1783" s="3"/>
+      <c r="B1783" s="7"/>
+    </row>
+    <row r="1784" ht="15.75" customHeight="1">
+      <c r="A1784" s="3"/>
+      <c r="B1784" s="7"/>
+    </row>
+    <row r="1785" ht="15.75" customHeight="1">
+      <c r="A1785" s="3"/>
+      <c r="B1785" s="7"/>
+    </row>
+    <row r="1786" ht="15.75" customHeight="1">
+      <c r="A1786" s="3"/>
+      <c r="B1786" s="7"/>
+    </row>
+    <row r="1787" ht="15.75" customHeight="1">
+      <c r="A1787" s="3"/>
+      <c r="B1787" s="7"/>
+    </row>
+    <row r="1788" ht="15.75" customHeight="1">
+      <c r="A1788" s="3"/>
+      <c r="B1788" s="7"/>
+    </row>
+    <row r="1789" ht="15.75" customHeight="1">
+      <c r="A1789" s="3"/>
+      <c r="B1789" s="7"/>
+    </row>
+    <row r="1790" ht="15.75" customHeight="1">
+      <c r="A1790" s="3"/>
+      <c r="B1790" s="7"/>
+    </row>
+    <row r="1791" ht="15.75" customHeight="1">
+      <c r="A1791" s="3"/>
+      <c r="B1791" s="7"/>
+    </row>
+    <row r="1792" ht="15.75" customHeight="1">
+      <c r="A1792" s="3"/>
+      <c r="B1792" s="7"/>
+    </row>
+    <row r="1793" ht="15.75" customHeight="1">
+      <c r="A1793" s="3"/>
+      <c r="B1793" s="7"/>
+    </row>
+    <row r="1794" ht="15.75" customHeight="1">
+      <c r="A1794" s="3"/>
+      <c r="B1794" s="7"/>
+    </row>
+    <row r="1795" ht="15.75" customHeight="1">
+      <c r="A1795" s="3"/>
+      <c r="B1795" s="7"/>
+    </row>
+    <row r="1796" ht="15.75" customHeight="1">
+      <c r="A1796" s="3"/>
+      <c r="B1796" s="7"/>
+    </row>
+    <row r="1797" ht="15.75" customHeight="1">
+      <c r="A1797" s="3"/>
+      <c r="B1797" s="7"/>
+    </row>
+    <row r="1798" ht="15.75" customHeight="1">
+      <c r="A1798" s="3"/>
+      <c r="B1798" s="7"/>
+    </row>
+    <row r="1799" ht="15.75" customHeight="1">
+      <c r="A1799" s="3"/>
+      <c r="B1799" s="7"/>
+    </row>
+    <row r="1800" ht="15.75" customHeight="1">
+      <c r="A1800" s="3"/>
+      <c r="B1800" s="7"/>
+    </row>
+    <row r="1801" ht="15.75" customHeight="1">
+      <c r="A1801" s="3"/>
+      <c r="B1801" s="7"/>
+    </row>
+    <row r="1802" ht="15.75" customHeight="1">
+      <c r="A1802" s="3"/>
+      <c r="B1802" s="7"/>
+    </row>
+    <row r="1803" ht="15.75" customHeight="1">
+      <c r="A1803" s="3"/>
+      <c r="B1803" s="7"/>
+    </row>
+    <row r="1804" ht="15.75" customHeight="1">
+      <c r="A1804" s="3"/>
+      <c r="B1804" s="7"/>
+    </row>
+    <row r="1805" ht="15.75" customHeight="1">
+      <c r="A1805" s="3"/>
+      <c r="B1805" s="7"/>
+    </row>
+    <row r="1806" ht="15.75" customHeight="1">
+      <c r="A1806" s="3"/>
+      <c r="B1806" s="7"/>
+    </row>
+    <row r="1807" ht="15.75" customHeight="1">
+      <c r="A1807" s="3"/>
+      <c r="B1807" s="7"/>
+    </row>
+    <row r="1808" ht="15.75" customHeight="1">
+      <c r="A1808" s="3"/>
+      <c r="B1808" s="7"/>
+    </row>
+    <row r="1809" ht="15.75" customHeight="1">
+      <c r="A1809" s="3"/>
+      <c r="B1809" s="7"/>
+    </row>
+    <row r="1810" ht="15.75" customHeight="1">
+      <c r="A1810" s="3"/>
+      <c r="B1810" s="7"/>
+    </row>
+    <row r="1811" ht="15.75" customHeight="1">
+      <c r="A1811" s="3"/>
+      <c r="B1811" s="7"/>
+    </row>
+    <row r="1812" ht="15.75" customHeight="1">
+      <c r="A1812" s="3"/>
+      <c r="B1812" s="7"/>
+    </row>
+    <row r="1813" ht="15.75" customHeight="1">
+      <c r="A1813" s="3"/>
+      <c r="B1813" s="7"/>
+    </row>
+    <row r="1814" ht="15.75" customHeight="1">
+      <c r="A1814" s="3"/>
+      <c r="B1814" s="7"/>
+    </row>
+    <row r="1815" ht="15.75" customHeight="1">
+      <c r="A1815" s="3"/>
+      <c r="B1815" s="7"/>
+    </row>
+    <row r="1816" ht="15.75" customHeight="1">
+      <c r="A1816" s="3"/>
+      <c r="B1816" s="7"/>
+    </row>
+    <row r="1817" ht="15.75" customHeight="1">
+      <c r="A1817" s="3"/>
+      <c r="B1817" s="7"/>
+    </row>
+    <row r="1818" ht="15.75" customHeight="1">
+      <c r="A1818" s="3"/>
+      <c r="B1818" s="7"/>
+    </row>
+    <row r="1819" ht="15.75" customHeight="1">
+      <c r="A1819" s="3"/>
+      <c r="B1819" s="7"/>
+    </row>
+    <row r="1820" ht="15.75" customHeight="1">
+      <c r="A1820" s="3"/>
+      <c r="B1820" s="7"/>
+    </row>
+    <row r="1821" ht="15.75" customHeight="1">
+      <c r="A1821" s="3"/>
+      <c r="B1821" s="7"/>
+    </row>
+    <row r="1822" ht="15.75" customHeight="1">
+      <c r="A1822" s="3"/>
+      <c r="B1822" s="7"/>
+    </row>
+    <row r="1823" ht="15.75" customHeight="1">
+      <c r="A1823" s="3"/>
+      <c r="B1823" s="7"/>
+    </row>
+    <row r="1824" ht="15.75" customHeight="1">
+      <c r="A1824" s="3"/>
+      <c r="B1824" s="7"/>
+    </row>
+    <row r="1825" ht="15.75" customHeight="1">
+      <c r="A1825" s="3"/>
+      <c r="B1825" s="7"/>
+    </row>
+    <row r="1826" ht="15.75" customHeight="1">
+      <c r="A1826" s="3"/>
+      <c r="B1826" s="7"/>
+    </row>
+    <row r="1827" ht="15.75" customHeight="1">
+      <c r="A1827" s="3"/>
+      <c r="B1827" s="7"/>
+    </row>
+    <row r="1828" ht="15.75" customHeight="1">
+      <c r="A1828" s="3"/>
+      <c r="B1828" s="7"/>
+    </row>
+    <row r="1829" ht="15.75" customHeight="1">
+      <c r="A1829" s="3"/>
+      <c r="B1829" s="7"/>
+    </row>
+    <row r="1830" ht="15.75" customHeight="1">
+      <c r="A1830" s="3"/>
+      <c r="B1830" s="7"/>
+    </row>
+    <row r="1831" ht="15.75" customHeight="1">
+      <c r="A1831" s="3"/>
+      <c r="B1831" s="7"/>
+    </row>
+    <row r="1832" ht="15.75" customHeight="1">
+      <c r="A1832" s="3"/>
+      <c r="B1832" s="7"/>
+    </row>
+    <row r="1833" ht="15.75" customHeight="1">
+      <c r="A1833" s="3"/>
+      <c r="B1833" s="7"/>
+    </row>
+    <row r="1834" ht="15.75" customHeight="1">
+      <c r="A1834" s="3"/>
+      <c r="B1834" s="7"/>
+    </row>
+    <row r="1835" ht="15.75" customHeight="1">
+      <c r="A1835" s="3"/>
+      <c r="B1835" s="7"/>
+    </row>
+    <row r="1836" ht="15.75" customHeight="1">
+      <c r="A1836" s="3"/>
+      <c r="B1836" s="7"/>
+    </row>
+    <row r="1837" ht="15.75" customHeight="1">
+      <c r="A1837" s="3"/>
+      <c r="B1837" s="7"/>
+    </row>
+    <row r="1838" ht="15.75" customHeight="1">
+      <c r="A1838" s="3"/>
+      <c r="B1838" s="7"/>
+    </row>
+    <row r="1839" ht="15.75" customHeight="1">
+      <c r="A1839" s="3"/>
+      <c r="B1839" s="7"/>
+    </row>
+    <row r="1840" ht="15.75" customHeight="1">
+      <c r="A1840" s="3"/>
+      <c r="B1840" s="7"/>
+    </row>
+    <row r="1841" ht="15.75" customHeight="1">
+      <c r="A1841" s="3"/>
+      <c r="B1841" s="7"/>
+    </row>
+    <row r="1842" ht="15.75" customHeight="1">
+      <c r="A1842" s="3"/>
+      <c r="B1842" s="7"/>
+    </row>
+    <row r="1843" ht="15.75" customHeight="1">
+      <c r="A1843" s="3"/>
+      <c r="B1843" s="7"/>
+    </row>
+    <row r="1844" ht="15.75" customHeight="1">
+      <c r="A1844" s="3"/>
+      <c r="B1844" s="7"/>
+    </row>
+    <row r="1845" ht="15.75" customHeight="1">
+      <c r="A1845" s="3"/>
+      <c r="B1845" s="7"/>
+    </row>
+    <row r="1846" ht="15.75" customHeight="1">
+      <c r="A1846" s="3"/>
+      <c r="B1846" s="7"/>
+    </row>
+    <row r="1847" ht="15.75" customHeight="1">
+      <c r="A1847" s="3"/>
+      <c r="B1847" s="7"/>
+    </row>
+    <row r="1848" ht="15.75" customHeight="1">
+      <c r="A1848" s="3"/>
+      <c r="B1848" s="7"/>
+    </row>
+    <row r="1849" ht="15.75" customHeight="1">
+      <c r="A1849" s="3"/>
+      <c r="B1849" s="7"/>
+    </row>
+    <row r="1850" ht="15.75" customHeight="1">
+      <c r="A1850" s="3"/>
+      <c r="B1850" s="7"/>
+    </row>
+    <row r="1851" ht="15.75" customHeight="1">
+      <c r="A1851" s="3"/>
+      <c r="B1851" s="7"/>
+    </row>
+    <row r="1852" ht="15.75" customHeight="1">
+      <c r="A1852" s="3"/>
+      <c r="B1852" s="7"/>
+    </row>
+    <row r="1853" ht="15.75" customHeight="1">
+      <c r="A1853" s="3"/>
+      <c r="B1853" s="7"/>
+    </row>
+    <row r="1854" ht="15.75" customHeight="1">
+      <c r="A1854" s="3"/>
+      <c r="B1854" s="7"/>
+    </row>
+    <row r="1855" ht="15.75" customHeight="1">
+      <c r="A1855" s="3"/>
+      <c r="B1855" s="7"/>
+    </row>
+    <row r="1856" ht="15.75" customHeight="1">
+      <c r="A1856" s="3"/>
+      <c r="B1856" s="7"/>
+    </row>
+    <row r="1857" ht="15.75" customHeight="1">
+      <c r="A1857" s="3"/>
+      <c r="B1857" s="7"/>
+    </row>
+    <row r="1858" ht="15.75" customHeight="1">
+      <c r="A1858" s="3"/>
+      <c r="B1858" s="7"/>
+    </row>
+    <row r="1859" ht="15.75" customHeight="1">
+      <c r="A1859" s="3"/>
+      <c r="B1859" s="7"/>
+    </row>
+    <row r="1860" ht="15.75" customHeight="1">
+      <c r="A1860" s="3"/>
+      <c r="B1860" s="7"/>
+    </row>
+    <row r="1861" ht="15.75" customHeight="1">
+      <c r="A1861" s="3"/>
+      <c r="B1861" s="7"/>
+    </row>
+    <row r="1862" ht="15.75" customHeight="1">
+      <c r="A1862" s="3"/>
+      <c r="B1862" s="7"/>
+    </row>
+    <row r="1863" ht="15.75" customHeight="1">
+      <c r="A1863" s="3"/>
+      <c r="B1863" s="7"/>
+    </row>
+    <row r="1864" ht="15.75" customHeight="1">
+      <c r="A1864" s="3"/>
+      <c r="B1864" s="7"/>
+    </row>
+    <row r="1865" ht="15.75" customHeight="1">
+      <c r="A1865" s="3"/>
+      <c r="B1865" s="7"/>
+    </row>
+    <row r="1866" ht="15.75" customHeight="1">
+      <c r="A1866" s="3"/>
+      <c r="B1866" s="7"/>
+    </row>
+    <row r="1867" ht="15.75" customHeight="1">
+      <c r="A1867" s="3"/>
+      <c r="B1867" s="7"/>
+    </row>
+    <row r="1868" ht="15.75" customHeight="1">
+      <c r="A1868" s="3"/>
+      <c r="B1868" s="7"/>
+    </row>
+    <row r="1869" ht="15.75" customHeight="1">
+      <c r="A1869" s="3"/>
+      <c r="B1869" s="7"/>
+    </row>
+    <row r="1870" ht="15.75" customHeight="1">
+      <c r="A1870" s="3"/>
+      <c r="B1870" s="7"/>
+    </row>
+    <row r="1871" ht="15.75" customHeight="1">
+      <c r="A1871" s="3"/>
+      <c r="B1871" s="7"/>
+    </row>
+    <row r="1872" ht="15.75" customHeight="1">
+      <c r="A1872" s="3"/>
+      <c r="B1872" s="7"/>
+    </row>
+    <row r="1873" ht="15.75" customHeight="1">
+      <c r="A1873" s="3"/>
+      <c r="B1873" s="7"/>
+    </row>
+    <row r="1874" ht="15.75" customHeight="1">
+      <c r="A1874" s="3"/>
+      <c r="B1874" s="7"/>
+    </row>
+    <row r="1875" ht="15.75" customHeight="1">
+      <c r="A1875" s="3"/>
+      <c r="B1875" s="7"/>
+    </row>
+    <row r="1876" ht="15.75" customHeight="1">
+      <c r="A1876" s="3"/>
+      <c r="B1876" s="7"/>
+    </row>
+    <row r="1877" ht="15.75" customHeight="1">
+      <c r="A1877" s="3"/>
+      <c r="B1877" s="7"/>
+    </row>
+    <row r="1878" ht="15.75" customHeight="1">
+      <c r="A1878" s="3"/>
+      <c r="B1878" s="7"/>
+    </row>
+    <row r="1879" ht="15.75" customHeight="1">
+      <c r="A1879" s="3"/>
+      <c r="B1879" s="7"/>
+    </row>
+    <row r="1880" ht="15.75" customHeight="1">
+      <c r="A1880" s="3"/>
+      <c r="B1880" s="7"/>
+    </row>
+    <row r="1881" ht="15.75" customHeight="1">
+      <c r="A1881" s="3"/>
+      <c r="B1881" s="7"/>
+    </row>
+    <row r="1882" ht="15.75" customHeight="1">
+      <c r="A1882" s="3"/>
+      <c r="B1882" s="7"/>
+    </row>
+    <row r="1883" ht="15.75" customHeight="1">
+      <c r="A1883" s="3"/>
+      <c r="B1883" s="7"/>
+    </row>
+    <row r="1884" ht="15.75" customHeight="1">
+      <c r="A1884" s="3"/>
+      <c r="B1884" s="7"/>
+    </row>
+    <row r="1885" ht="15.75" customHeight="1">
+      <c r="A1885" s="3"/>
+      <c r="B1885" s="7"/>
+    </row>
+    <row r="1886" ht="15.75" customHeight="1">
+      <c r="A1886" s="3"/>
+      <c r="B1886" s="7"/>
+    </row>
+    <row r="1887" ht="15.75" customHeight="1">
+      <c r="A1887" s="3"/>
+      <c r="B1887" s="7"/>
+    </row>
+    <row r="1888" ht="15.75" customHeight="1">
+      <c r="A1888" s="3"/>
+      <c r="B1888" s="7"/>
+    </row>
+    <row r="1889" ht="15.75" customHeight="1">
+      <c r="A1889" s="3"/>
+      <c r="B1889" s="7"/>
+    </row>
+    <row r="1890" ht="15.75" customHeight="1">
+      <c r="A1890" s="3"/>
+      <c r="B1890" s="7"/>
+    </row>
+    <row r="1891" ht="15.75" customHeight="1">
+      <c r="A1891" s="3"/>
+      <c r="B1891" s="7"/>
+    </row>
+    <row r="1892" ht="15.75" customHeight="1">
+      <c r="A1892" s="3"/>
+      <c r="B1892" s="7"/>
+    </row>
+    <row r="1893" ht="15.75" customHeight="1">
+      <c r="A1893" s="3"/>
+      <c r="B1893" s="7"/>
+    </row>
+    <row r="1894" ht="15.75" customHeight="1">
+      <c r="A1894" s="3"/>
+      <c r="B1894" s="7"/>
+    </row>
+    <row r="1895" ht="15.75" customHeight="1">
+      <c r="A1895" s="3"/>
+      <c r="B1895" s="7"/>
+    </row>
+    <row r="1896" ht="15.75" customHeight="1">
+      <c r="A1896" s="3"/>
+      <c r="B1896" s="7"/>
+    </row>
+    <row r="1897" ht="15.75" customHeight="1">
+      <c r="A1897" s="3"/>
+      <c r="B1897" s="7"/>
+    </row>
+    <row r="1898" ht="15.75" customHeight="1">
+      <c r="A1898" s="3"/>
+      <c r="B1898" s="7"/>
+    </row>
+    <row r="1899" ht="15.75" customHeight="1">
+      <c r="A1899" s="3"/>
+      <c r="B1899" s="7"/>
+    </row>
+    <row r="1900" ht="15.75" customHeight="1">
+      <c r="A1900" s="3"/>
+      <c r="B1900" s="7"/>
+    </row>
+    <row r="1901" ht="15.75" customHeight="1">
+      <c r="A1901" s="3"/>
+      <c r="B1901" s="7"/>
+    </row>
+    <row r="1902" ht="15.75" customHeight="1">
+      <c r="A1902" s="3"/>
+      <c r="B1902" s="7"/>
+    </row>
+    <row r="1903" ht="15.75" customHeight="1">
+      <c r="A1903" s="3"/>
+      <c r="B1903" s="7"/>
+    </row>
+    <row r="1904" ht="15.75" customHeight="1">
+      <c r="A1904" s="3"/>
+      <c r="B1904" s="7"/>
+    </row>
+    <row r="1905" ht="15.75" customHeight="1">
+      <c r="A1905" s="3"/>
+      <c r="B1905" s="7"/>
+    </row>
+    <row r="1906" ht="15.75" customHeight="1">
+      <c r="A1906" s="3"/>
+      <c r="B1906" s="7"/>
+    </row>
+    <row r="1907" ht="15.75" customHeight="1">
+      <c r="A1907" s="3"/>
+      <c r="B1907" s="7"/>
+    </row>
+    <row r="1908" ht="15.75" customHeight="1">
+      <c r="A1908" s="3"/>
+      <c r="B1908" s="7"/>
+    </row>
+    <row r="1909" ht="15.75" customHeight="1">
+      <c r="A1909" s="3"/>
+      <c r="B1909" s="7"/>
+    </row>
+    <row r="1910" ht="15.75" customHeight="1">
+      <c r="A1910" s="3"/>
+      <c r="B1910" s="7"/>
+    </row>
+    <row r="1911" ht="15.75" customHeight="1">
+      <c r="A1911" s="3"/>
+      <c r="B1911" s="7"/>
+    </row>
+    <row r="1912" ht="15.75" customHeight="1">
+      <c r="A1912" s="3"/>
+      <c r="B1912" s="7"/>
+    </row>
+    <row r="1913" ht="15.75" customHeight="1">
+      <c r="A1913" s="3"/>
+      <c r="B1913" s="7"/>
+    </row>
+    <row r="1914" ht="15.75" customHeight="1">
+      <c r="A1914" s="3"/>
+      <c r="B1914" s="7"/>
+    </row>
+    <row r="1915" ht="15.75" customHeight="1">
+      <c r="A1915" s="3"/>
+      <c r="B1915" s="7"/>
+    </row>
+    <row r="1916" ht="15.75" customHeight="1">
+      <c r="A1916" s="3"/>
+      <c r="B1916" s="7"/>
+    </row>
+    <row r="1917" ht="15.75" customHeight="1">
+      <c r="A1917" s="3"/>
+      <c r="B1917" s="7"/>
+    </row>
+    <row r="1918" ht="15.75" customHeight="1">
+      <c r="A1918" s="3"/>
+      <c r="B1918" s="7"/>
+    </row>
+    <row r="1919" ht="15.75" customHeight="1">
+      <c r="A1919" s="3"/>
+      <c r="B1919" s="7"/>
+    </row>
+    <row r="1920" ht="15.75" customHeight="1">
+      <c r="A1920" s="3"/>
+      <c r="B1920" s="7"/>
+    </row>
+    <row r="1921" ht="15.75" customHeight="1">
+      <c r="A1921" s="3"/>
+      <c r="B1921" s="7"/>
+    </row>
+    <row r="1922" ht="15.75" customHeight="1">
+      <c r="A1922" s="3"/>
+      <c r="B1922" s="7"/>
+    </row>
+    <row r="1923" ht="15.75" customHeight="1">
+      <c r="A1923" s="3"/>
+      <c r="B1923" s="7"/>
+    </row>
+    <row r="1924" ht="15.75" customHeight="1">
+      <c r="A1924" s="3"/>
+      <c r="B1924" s="7"/>
+    </row>
+    <row r="1925" ht="15.75" customHeight="1">
+      <c r="A1925" s="3"/>
+      <c r="B1925" s="7"/>
+    </row>
+    <row r="1926" ht="15.75" customHeight="1">
+      <c r="A1926" s="3"/>
+      <c r="B1926" s="7"/>
+    </row>
+    <row r="1927" ht="15.75" customHeight="1">
+      <c r="A1927" s="3"/>
+      <c r="B1927" s="7"/>
+    </row>
+    <row r="1928" ht="15.75" customHeight="1">
+      <c r="A1928" s="3"/>
+      <c r="B1928" s="7"/>
+    </row>
+    <row r="1929" ht="15.75" customHeight="1">
+      <c r="A1929" s="3"/>
+      <c r="B1929" s="7"/>
+    </row>
+    <row r="1930" ht="15.75" customHeight="1">
+      <c r="A1930" s="3"/>
+      <c r="B1930" s="7"/>
+    </row>
+    <row r="1931" ht="15.75" customHeight="1">
+      <c r="A1931" s="3"/>
+      <c r="B1931" s="7"/>
+    </row>
+    <row r="1932" ht="15.75" customHeight="1">
+      <c r="A1932" s="3"/>
+      <c r="B1932" s="7"/>
+    </row>
+    <row r="1933" ht="15.75" customHeight="1">
+      <c r="A1933" s="3"/>
+      <c r="B1933" s="7"/>
+    </row>
+    <row r="1934" ht="15.75" customHeight="1">
+      <c r="A1934" s="3"/>
+      <c r="B1934" s="7"/>
+    </row>
+    <row r="1935" ht="15.75" customHeight="1">
+      <c r="A1935" s="3"/>
+      <c r="B1935" s="7"/>
+    </row>
+    <row r="1936" ht="15.75" customHeight="1">
+      <c r="A1936" s="3"/>
+      <c r="B1936" s="7"/>
+    </row>
+    <row r="1937" ht="15.75" customHeight="1">
+      <c r="A1937" s="3"/>
+      <c r="B1937" s="7"/>
+    </row>
+    <row r="1938" ht="15.75" customHeight="1">
+      <c r="A1938" s="3"/>
+      <c r="B1938" s="7"/>
+    </row>
+    <row r="1939" ht="15.75" customHeight="1">
+      <c r="A1939" s="3"/>
+      <c r="B1939" s="7"/>
+    </row>
+    <row r="1940" ht="15.75" customHeight="1">
+      <c r="A1940" s="3"/>
+      <c r="B1940" s="7"/>
+    </row>
+    <row r="1941" ht="15.75" customHeight="1">
+      <c r="A1941" s="3"/>
+      <c r="B1941" s="7"/>
+    </row>
+    <row r="1942" ht="15.75" customHeight="1">
+      <c r="A1942" s="3"/>
+      <c r="B1942" s="7"/>
+    </row>
+    <row r="1943" ht="15.75" customHeight="1">
+      <c r="A1943" s="3"/>
+      <c r="B1943" s="7"/>
+    </row>
+    <row r="1944" ht="15.75" customHeight="1">
+      <c r="A1944" s="3"/>
+      <c r="B1944" s="7"/>
+    </row>
+    <row r="1945" ht="15.75" customHeight="1">
+      <c r="A1945" s="3"/>
+      <c r="B1945" s="7"/>
+    </row>
+    <row r="1946" ht="15.75" customHeight="1">
+      <c r="A1946" s="3"/>
+      <c r="B1946" s="7"/>
+    </row>
+    <row r="1947" ht="15.75" customHeight="1">
+      <c r="A1947" s="3"/>
+      <c r="B1947" s="7"/>
+    </row>
+    <row r="1948" ht="15.75" customHeight="1">
+      <c r="A1948" s="3"/>
+      <c r="B1948" s="7"/>
+    </row>
+    <row r="1949" ht="15.75" customHeight="1">
+      <c r="A1949" s="3"/>
+      <c r="B1949" s="7"/>
+    </row>
+    <row r="1950" ht="15.75" customHeight="1">
+      <c r="A1950" s="3"/>
+      <c r="B1950" s="7"/>
+    </row>
+    <row r="1951" ht="15.75" customHeight="1">
+      <c r="A1951" s="3"/>
+      <c r="B1951" s="7"/>
+    </row>
+    <row r="1952" ht="15.75" customHeight="1">
+      <c r="A1952" s="3"/>
+      <c r="B1952" s="7"/>
+    </row>
+    <row r="1953" ht="15.75" customHeight="1">
+      <c r="A1953" s="3"/>
+      <c r="B1953" s="7"/>
+    </row>
+    <row r="1954" ht="15.75" customHeight="1">
+      <c r="A1954" s="3"/>
+      <c r="B1954" s="7"/>
+    </row>
+    <row r="1955" ht="15.75" customHeight="1">
+      <c r="A1955" s="3"/>
+      <c r="B1955" s="7"/>
+    </row>
+    <row r="1956" ht="15.75" customHeight="1">
+      <c r="A1956" s="3"/>
+      <c r="B1956" s="7"/>
+    </row>
+    <row r="1957" ht="15.75" customHeight="1">
+      <c r="A1957" s="3"/>
+      <c r="B1957" s="7"/>
+    </row>
+    <row r="1958" ht="15.75" customHeight="1">
+      <c r="A1958" s="3"/>
+      <c r="B1958" s="7"/>
+    </row>
+    <row r="1959" ht="15.75" customHeight="1">
+      <c r="A1959" s="3"/>
+      <c r="B1959" s="7"/>
+    </row>
+    <row r="1960" ht="15.75" customHeight="1">
+      <c r="A1960" s="3"/>
+      <c r="B1960" s="7"/>
+    </row>
+    <row r="1961" ht="15.75" customHeight="1">
+      <c r="A1961" s="3"/>
+      <c r="B1961" s="7"/>
+    </row>
+    <row r="1962" ht="15.75" customHeight="1">
+      <c r="A1962" s="3"/>
+      <c r="B1962" s="7"/>
+    </row>
+    <row r="1963" ht="15.75" customHeight="1">
+      <c r="A1963" s="3"/>
+      <c r="B1963" s="7"/>
+    </row>
+    <row r="1964" ht="15.75" customHeight="1">
+      <c r="A1964" s="3"/>
+      <c r="B1964" s="7"/>
+    </row>
+    <row r="1965" ht="15.75" customHeight="1">
+      <c r="A1965" s="3"/>
+      <c r="B1965" s="7"/>
+    </row>
+    <row r="1966" ht="15.75" customHeight="1">
+      <c r="A1966" s="3"/>
+      <c r="B1966" s="7"/>
+    </row>
+    <row r="1967" ht="15.75" customHeight="1">
+      <c r="A1967" s="3"/>
+      <c r="B1967" s="7"/>
+    </row>
+    <row r="1968" ht="15.75" customHeight="1">
+      <c r="A1968" s="3"/>
+      <c r="B1968" s="7"/>
+    </row>
+    <row r="1969" ht="15.75" customHeight="1">
+      <c r="A1969" s="3"/>
+      <c r="B1969" s="7"/>
+    </row>
+    <row r="1970" ht="15.75" customHeight="1">
+      <c r="A1970" s="3"/>
+      <c r="B1970" s="7"/>
+    </row>
+    <row r="1971" ht="15.75" customHeight="1">
+      <c r="A1971" s="3"/>
+      <c r="B1971" s="7"/>
+    </row>
+    <row r="1972" ht="15.75" customHeight="1">
+      <c r="A1972" s="3"/>
+      <c r="B1972" s="7"/>
+    </row>
+    <row r="1973" ht="15.75" customHeight="1">
+      <c r="A1973" s="3"/>
+      <c r="B1973" s="7"/>
+    </row>
+    <row r="1974" ht="15.75" customHeight="1">
+      <c r="A1974" s="3"/>
+      <c r="B1974" s="7"/>
+    </row>
+    <row r="1975" ht="15.75" customHeight="1">
+      <c r="A1975" s="3"/>
+      <c r="B1975" s="7"/>
+    </row>
+    <row r="1976" ht="15.75" customHeight="1">
+      <c r="A1976" s="3"/>
+      <c r="B1976" s="7"/>
+    </row>
+    <row r="1977" ht="15.75" customHeight="1">
+      <c r="A1977" s="3"/>
+      <c r="B1977" s="7"/>
+    </row>
+    <row r="1978" ht="15.75" customHeight="1">
+      <c r="A1978" s="3"/>
+      <c r="B1978" s="7"/>
+    </row>
+    <row r="1979" ht="15.75" customHeight="1">
+      <c r="A1979" s="3"/>
+      <c r="B1979" s="7"/>
+    </row>
+    <row r="1980" ht="15.75" customHeight="1">
+      <c r="A1980" s="3"/>
+      <c r="B1980" s="7"/>
+    </row>
+    <row r="1981" ht="15.75" customHeight="1">
+      <c r="A1981" s="3"/>
+      <c r="B1981" s="7"/>
+    </row>
+    <row r="1982" ht="15.75" customHeight="1">
+      <c r="A1982" s="3"/>
+      <c r="B1982" s="7"/>
+    </row>
+    <row r="1983" ht="15.75" customHeight="1">
+      <c r="A1983" s="3"/>
+      <c r="B1983" s="7"/>
+    </row>
+    <row r="1984" ht="15.75" customHeight="1">
+      <c r="A1984" s="3"/>
+      <c r="B1984" s="7"/>
+    </row>
+    <row r="1985" ht="15.75" customHeight="1">
+      <c r="A1985" s="3"/>
+      <c r="B1985" s="7"/>
+    </row>
+    <row r="1986" ht="15.75" customHeight="1">
+      <c r="A1986" s="3"/>
+      <c r="B1986" s="7"/>
+    </row>
+    <row r="1987" ht="15.75" customHeight="1">
+      <c r="A1987" s="3"/>
+      <c r="B1987" s="7"/>
+    </row>
+    <row r="1988" ht="15.75" customHeight="1">
+      <c r="A1988" s="3"/>
+      <c r="B1988" s="7"/>
+    </row>
+    <row r="1989" ht="15.75" customHeight="1">
+      <c r="A1989" s="3"/>
+      <c r="B1989" s="7"/>
+    </row>
+    <row r="1990" ht="15.75" customHeight="1">
+      <c r="A1990" s="3"/>
+      <c r="B1990" s="7"/>
+    </row>
+    <row r="1991" ht="15.75" customHeight="1">
+      <c r="A1991" s="3"/>
+      <c r="B1991" s="7"/>
+    </row>
+    <row r="1992" ht="15.75" customHeight="1">
+      <c r="A1992" s="3"/>
+      <c r="B1992" s="7"/>
+    </row>
+    <row r="1993" ht="15.75" customHeight="1">
+      <c r="A1993" s="3"/>
+      <c r="B1993" s="7"/>
+    </row>
+    <row r="1994" ht="15.75" customHeight="1">
+      <c r="A1994" s="3"/>
+      <c r="B1994" s="7"/>
+    </row>
+    <row r="1995" ht="15.75" customHeight="1">
+      <c r="A1995" s="3"/>
+      <c r="B1995" s="7"/>
+    </row>
+    <row r="1996" ht="15.75" customHeight="1">
+      <c r="A1996" s="3"/>
+      <c r="B1996" s="7"/>
+    </row>
+    <row r="1997" ht="15.75" customHeight="1">
+      <c r="A1997" s="3"/>
+      <c r="B1997" s="7"/>
+    </row>
+    <row r="1998" ht="15.75" customHeight="1">
+      <c r="A1998" s="3"/>
+      <c r="B1998" s="7"/>
+    </row>
+    <row r="1999" ht="15.75" customHeight="1">
+      <c r="A1999" s="3"/>
+      <c r="B1999" s="7"/>
+    </row>
+    <row r="2000" ht="15.75" customHeight="1">
+      <c r="A2000" s="3"/>
+      <c r="B2000" s="7"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
